--- a/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
+++ b/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
@@ -5739,7 +5739,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5938,7 +5938,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6059,7 +6059,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6180,7 +6180,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6301,7 +6301,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6422,7 +6422,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
+++ b/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
@@ -4338,7 +4338,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -4357,7 +4357,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
+++ b/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
@@ -4642,7 +4642,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -4661,6 +4661,369 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics v20.1 IF_CapexIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（經橋接表；唯讀）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">itpg_vr</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本支出（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架未另訂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：同 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">vr26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年部署中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">世代占比（混合每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數值用）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interested-party</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">avc/dist/20261025_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
@@ -4680,7 +5043,171 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E10</t>
+      <t xml:space="preserve">In!D11:F11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TrendForce 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin 22%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（經 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/memory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；與奇鋐、台達電模型相同）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">racks_gb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">架</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晶片內容橋接表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E6</t>
     </r>
     <r>
       <rPr>
@@ -4718,7 +5245,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">H10</t>
+      <t xml:space="preserve">H6</t>
     </r>
     <r>
       <rPr>
@@ -4758,20 +5285,20 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Tokenomics v20.1 IF_CapexIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（經橋接表；唯讀）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">itpg_vr</t>
+      <t xml:space="preserve">Tokenomics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（經橋接表）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">racks_vr</t>
   </si>
   <si>
     <r>
@@ -4791,16 +5318,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">GW IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資本支出（</t>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架數（</t>
     </r>
     <r>
       <rPr>
@@ -4819,357 +5346,46 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin Ultra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架未另訂（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：同 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">vr26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年部署中 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">世代占比（混合每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">數值用）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interested-party</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!D11:F11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TrendForce 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組合 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin 22%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（經 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">markets/memory</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；與奇鋐、台達電模型相同）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">racks_gb</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架數（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">架</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+    <t xml:space="preserve">cool_gb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每架機架內液冷（運算匣＋交換匣，橋接表）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">US$K</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -5188,223 +5404,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!E6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tokenomics</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（經橋接表）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">racks_vr</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架數（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">cool_gb</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每架機架內液冷（運算匣＋交換匣，橋接表）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">US$K</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晶片內容橋接表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36254,7 +36254,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>31</v>
@@ -39416,7 +39416,7 @@
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">PL!D106</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">PL!E106</f>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">PL!D110</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="D8" s="13" t="n">
         <f aca="false">PL!E110</f>
@@ -39497,7 +39497,7 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">C8+C9</f>
-        <v>0.657628417556845</v>
+        <v>0.657628417556846</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">D8+D9</f>
@@ -39524,7 +39524,7 @@
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">1-C10</f>
-        <v>0.342371582443155</v>
+        <v>0.342371582443154</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">1-D10</f>
@@ -39532,7 +39532,7 @@
       </c>
       <c r="E11" s="13" t="n">
         <f aca="false">1-E10</f>
-        <v>0.408134424198839</v>
+        <v>0.408134424198838</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">1-F10</f>
@@ -39556,11 +39556,11 @@
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">PL!F111/fx</f>
-        <v>1.80338680509493</v>
+        <v>1.80338680509494</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">PL!G111/fx</f>
-        <v>2.18273910070319</v>
+        <v>2.1827391007032</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39580,11 +39580,11 @@
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">PL!F119</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="F13" s="17" t="n">
         <f aca="false">PL!G119</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39672,11 +39672,11 @@
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">E78</f>
-        <v>76.4908399924033</v>
+        <v>76.4908399924034</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">F78</f>
-        <v>108.647210224341</v>
+        <v>108.647210224342</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">G78</f>
@@ -39724,11 +39724,11 @@
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E73</f>
-        <v>61.6485709807633</v>
+        <v>61.6485709807634</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">F73</f>
-        <v>94.0589980696574</v>
+        <v>94.0589980696575</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">G73</f>
@@ -39900,7 +39900,7 @@
       </c>
       <c r="G13" s="13" t="n">
         <f aca="false">G89</f>
-        <v>0.222178769465522</v>
+        <v>0.222178769465523</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">F92</f>
-        <v>17.5442617511424</v>
+        <v>17.5442617511425</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">G92</f>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="G15" s="14" t="n">
         <f aca="false">G94</f>
-        <v>214.610421061672</v>
+        <v>214.610421061673</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40005,15 +40005,15 @@
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">E116</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">F116</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">G116</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40029,7 +40029,7 @@
       </c>
       <c r="E20" s="13" t="n">
         <f aca="false">E117</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F20" s="13" t="n">
         <f aca="false">F117</f>
@@ -40061,11 +40061,11 @@
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">F111</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">G111</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40225,7 +40225,7 @@
       </c>
       <c r="E27" s="13" t="n">
         <f aca="false">E127</f>
-        <v>0.199583425893515</v>
+        <v>0.199583425893516</v>
       </c>
       <c r="F27" s="13" t="n">
         <f aca="false">F127</f>
@@ -40253,7 +40253,7 @@
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E130</f>
-        <v>9.46076550392361</v>
+        <v>9.46076550392362</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">F130</f>
@@ -40305,11 +40305,11 @@
       </c>
       <c r="E30" s="13" t="n">
         <f aca="false">E133</f>
-        <v>0.92141973687635</v>
+        <v>0.921419736876353</v>
       </c>
       <c r="F30" s="13" t="n">
         <f aca="false">F133</f>
-        <v>0.159406685035449</v>
+        <v>0.159406685035448</v>
       </c>
       <c r="G30" s="13" t="n">
         <f aca="false">G133</f>
@@ -40338,7 +40338,7 @@
       </c>
       <c r="E33" s="18" t="n">
         <f aca="false">E154</f>
-        <v>50.0700238577904</v>
+        <v>50.0700238577905</v>
       </c>
       <c r="F33" s="18" t="n">
         <f aca="false">F154</f>
@@ -40346,7 +40346,7 @@
       </c>
       <c r="G33" s="18" t="n">
         <f aca="false">G154</f>
-        <v>48.1830905667014</v>
+        <v>48.1830905667015</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40362,15 +40362,15 @@
       </c>
       <c r="E34" s="13" t="n">
         <f aca="false">E155</f>
-        <v>0.310595048068207</v>
+        <v>0.310595048068208</v>
       </c>
       <c r="F34" s="13" t="n">
         <f aca="false">F155</f>
-        <v>-0.115417764206357</v>
+        <v>-0.115417764206358</v>
       </c>
       <c r="G34" s="13" t="n">
         <f aca="false">G155</f>
-        <v>0.087874109906257</v>
+        <v>0.0878741099062572</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="E35" s="18" t="n">
         <f aca="false">E149</f>
-        <v>35.2277548461504</v>
+        <v>35.2277548461505</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">F149</f>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="G35" s="18" t="n">
         <f aca="false">G149</f>
-        <v>33.8362324261256</v>
+        <v>33.8362324261257</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40510,7 +40510,7 @@
       </c>
       <c r="G39" s="13" t="n">
         <f aca="false">G156</f>
-        <v>0.702242882890316</v>
+        <v>0.702242882890317</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40586,7 +40586,7 @@
       </c>
       <c r="E42" s="18" t="n">
         <f aca="false">E168</f>
-        <v>7.02595703347203</v>
+        <v>7.02595703347204</v>
       </c>
       <c r="F42" s="18" t="n">
         <f aca="false">F168</f>
@@ -40594,7 +40594,7 @@
       </c>
       <c r="G42" s="18" t="n">
         <f aca="false">G168</f>
-        <v>6.38748917436167</v>
+        <v>6.38748917436168</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40614,15 +40614,15 @@
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">E170</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">F170</f>
-        <v>61.3363362449752</v>
+        <v>61.3363362449753</v>
       </c>
       <c r="G43" s="14" t="n">
         <f aca="false">G170</f>
-        <v>68.625980214193</v>
+        <v>68.6259802141931</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40638,7 +40638,7 @@
       </c>
       <c r="E44" s="13" t="n">
         <f aca="false">E171</f>
-        <v>0.426926025062102</v>
+        <v>0.426926025062105</v>
       </c>
       <c r="F44" s="13" t="n">
         <f aca="false">F171</f>
@@ -40726,7 +40726,7 @@
       </c>
       <c r="D63" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -40849,7 +40849,7 @@
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">D65*D66*D67/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E68" s="19" t="n">
         <f aca="false">E65*E66*E67/1000</f>
@@ -40897,7 +40897,7 @@
       </c>
       <c r="D70" s="13" t="n">
         <f aca="false">a26_lc/D69</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>461</v>
@@ -40936,7 +40936,7 @@
       </c>
       <c r="D72" s="13" t="n">
         <f aca="false">$D$70*D71</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E72" s="13" t="n">
         <f aca="false">$D$70*E71</f>
@@ -40968,11 +40968,11 @@
       </c>
       <c r="E73" s="18" t="n">
         <f aca="false">E69*E72</f>
-        <v>61.6485709807633</v>
+        <v>61.6485709807634</v>
       </c>
       <c r="F73" s="18" t="n">
         <f aca="false">F69*F72</f>
-        <v>94.0589980696574</v>
+        <v>94.0589980696575</v>
       </c>
       <c r="G73" s="18" t="n">
         <f aca="false">G69*G72</f>
@@ -41085,11 +41085,11 @@
       </c>
       <c r="E78" s="18" t="n">
         <f aca="false">E73+E75+E76+E77</f>
-        <v>76.4908399924033</v>
+        <v>76.4908399924034</v>
       </c>
       <c r="F78" s="18" t="n">
         <f aca="false">F73+F75+F76+F77</f>
-        <v>108.647210224341</v>
+        <v>108.647210224342</v>
       </c>
       <c r="G78" s="18" t="n">
         <f aca="false">G73+G75+G76+G77</f>
@@ -41217,7 +41217,7 @@
       </c>
       <c r="G84" s="18" t="n">
         <f aca="false">$D$83*G78+d_lc*G73</f>
-        <v>36.9650968154173</v>
+        <v>36.9650968154174</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41265,15 +41265,15 @@
       </c>
       <c r="E86" s="18" t="n">
         <f aca="false">D86*(1+MAX(0,phi*E79))</f>
-        <v>7.27250355028488</v>
+        <v>7.27250355028489</v>
       </c>
       <c r="F86" s="18" t="n">
         <f aca="false">E86*(1+MAX(0,phi*F79))</f>
-        <v>9.25976445439478</v>
+        <v>9.25976445439479</v>
       </c>
       <c r="G86" s="18" t="n">
         <f aca="false">F86*(1+MAX(0,phi*G79))</f>
-        <v>9.9715033293921</v>
+        <v>9.97150332939211</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41293,15 +41293,15 @@
       </c>
       <c r="E87" s="18" t="n">
         <f aca="false">E86+0*E78</f>
-        <v>7.27250355028488</v>
+        <v>7.27250355028489</v>
       </c>
       <c r="F87" s="18" t="n">
         <f aca="false">F86+0*F78</f>
-        <v>9.25976445439478</v>
+        <v>9.25976445439479</v>
       </c>
       <c r="G87" s="18" t="n">
         <f aca="false">G86+0*G78</f>
-        <v>9.9715033293921</v>
+        <v>9.97150332939211</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41357,7 +41357,7 @@
       </c>
       <c r="G89" s="13" t="n">
         <f aca="false">G88/G78</f>
-        <v>0.222178769465522</v>
+        <v>0.222178769465523</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41437,7 +41437,7 @@
       </c>
       <c r="F92" s="18" t="n">
         <f aca="false">(F88+F90)*F91</f>
-        <v>17.5442617511424</v>
+        <v>17.5442617511425</v>
       </c>
       <c r="G92" s="18" t="n">
         <f aca="false">(G88+G90)*G91</f>
@@ -41497,7 +41497,7 @@
       </c>
       <c r="G94" s="19" t="n">
         <f aca="false">G92/G93</f>
-        <v>214.610421061672</v>
+        <v>214.610421061673</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41569,7 +41569,7 @@
       </c>
       <c r="D101" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E101" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="D106" s="19" t="n">
         <f aca="false">D103*D104*D105/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E106" s="19" t="n">
         <f aca="false">E103*E104*E105/1000</f>
@@ -41740,7 +41740,7 @@
       </c>
       <c r="D108" s="13" t="n">
         <f aca="false">a26_lc/D107</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H108" s="7" t="s">
         <v>461</v>
@@ -41779,7 +41779,7 @@
       </c>
       <c r="D110" s="13" t="n">
         <f aca="false">$D$108*D109</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E110" s="13" t="n">
         <f aca="false">$D$108*E109</f>
@@ -41815,11 +41815,11 @@
       </c>
       <c r="F111" s="18" t="n">
         <f aca="false">F107*F110</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G111" s="18" t="n">
         <f aca="false">G107*G110</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41928,15 +41928,15 @@
       </c>
       <c r="E116" s="18" t="n">
         <f aca="false">E111+E113+E114+E115</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F116" s="18" t="n">
         <f aca="false">F111+F113+F114+F115</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G116" s="18" t="n">
         <f aca="false">G111+G113+G114+G115</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="E117" s="13" t="n">
         <f aca="false">E116/D116-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F117" s="13" t="n">
         <f aca="false">F116/E116-1</f>
@@ -42008,11 +42008,11 @@
       </c>
       <c r="F119" s="17" t="n">
         <f aca="false">F111/fx/F103*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G119" s="17" t="n">
         <f aca="false">G111/fx/G103*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42116,7 +42116,7 @@
       </c>
       <c r="G124" s="18" t="n">
         <f aca="false">F124*(1+MAX(0,phi*G117))</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42144,7 +42144,7 @@
       </c>
       <c r="G125" s="18" t="n">
         <f aca="false">G124+0*G116</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42168,11 +42168,11 @@
       </c>
       <c r="F126" s="18" t="n">
         <f aca="false">F122-F125</f>
-        <v>14.8228037443267</v>
+        <v>14.8228037443268</v>
       </c>
       <c r="G126" s="18" t="n">
         <f aca="false">G122-G125</f>
-        <v>17.7900852364066</v>
+        <v>17.7900852364067</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42192,7 +42192,7 @@
       </c>
       <c r="E127" s="13" t="n">
         <f aca="false">E126/E116</f>
-        <v>0.199583425893515</v>
+        <v>0.199583425893516</v>
       </c>
       <c r="F127" s="13" t="n">
         <f aca="false">F126/F116</f>
@@ -42276,7 +42276,7 @@
       </c>
       <c r="E130" s="18" t="n">
         <f aca="false">(E126+E128)*E129</f>
-        <v>9.46076550392361</v>
+        <v>9.46076550392362</v>
       </c>
       <c r="F130" s="18" t="n">
         <f aca="false">(F126+F128)*F129</f>
@@ -42356,11 +42356,11 @@
       </c>
       <c r="E133" s="13" t="n">
         <f aca="false">E132/D132-1</f>
-        <v>0.92141973687635</v>
+        <v>0.921419736876353</v>
       </c>
       <c r="F133" s="13" t="n">
         <f aca="false">F132/E132-1</f>
-        <v>0.159406685035449</v>
+        <v>0.159406685035448</v>
       </c>
       <c r="G133" s="13" t="n">
         <f aca="false">G132/F132-1</f>
@@ -42412,7 +42412,7 @@
       </c>
       <c r="D139" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E139" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -42535,7 +42535,7 @@
       </c>
       <c r="D144" s="19" t="n">
         <f aca="false">D141*D142*D143/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E144" s="19" t="n">
         <f aca="false">E141*E142*E143/1000</f>
@@ -42583,7 +42583,7 @@
       </c>
       <c r="D146" s="13" t="n">
         <f aca="false">a26_lc/D145</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H146" s="7" t="s">
         <v>461</v>
@@ -42622,7 +42622,7 @@
       </c>
       <c r="D148" s="13" t="n">
         <f aca="false">$D$146*D147</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E148" s="13" t="n">
         <f aca="false">$D$146*E147</f>
@@ -42654,7 +42654,7 @@
       </c>
       <c r="E149" s="18" t="n">
         <f aca="false">E145*E148</f>
-        <v>35.2277548461504</v>
+        <v>35.2277548461505</v>
       </c>
       <c r="F149" s="18" t="n">
         <f aca="false">F145*F148</f>
@@ -42662,7 +42662,7 @@
       </c>
       <c r="G149" s="18" t="n">
         <f aca="false">G145*G148</f>
-        <v>33.8362324261256</v>
+        <v>33.8362324261257</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="E154" s="18" t="n">
         <f aca="false">E149+E151+E152+E153</f>
-        <v>50.0700238577904</v>
+        <v>50.0700238577905</v>
       </c>
       <c r="F154" s="18" t="n">
         <f aca="false">F149+F151+F152+F153</f>
@@ -42779,7 +42779,7 @@
       </c>
       <c r="G154" s="18" t="n">
         <f aca="false">G149+G151+G152+G153</f>
-        <v>48.1830905667014</v>
+        <v>48.1830905667015</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42795,15 +42795,15 @@
       </c>
       <c r="E155" s="13" t="n">
         <f aca="false">E154/D154-1</f>
-        <v>0.310595048068207</v>
+        <v>0.310595048068208</v>
       </c>
       <c r="F155" s="13" t="n">
         <f aca="false">F154/E154-1</f>
-        <v>-0.115417764206357</v>
+        <v>-0.115417764206358</v>
       </c>
       <c r="G155" s="13" t="n">
         <f aca="false">G154/F154-1</f>
-        <v>0.087874109906257</v>
+        <v>0.0878741099062572</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42831,7 +42831,7 @@
       </c>
       <c r="G156" s="13" t="n">
         <f aca="false">G149/G154</f>
-        <v>0.702242882890316</v>
+        <v>0.702242882890317</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42959,7 +42959,7 @@
       </c>
       <c r="G162" s="18" t="n">
         <f aca="false">F162*(1+MAX(0,phi*G155))</f>
-        <v>5.59521299856242</v>
+        <v>5.59521299856243</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42987,7 +42987,7 @@
       </c>
       <c r="G163" s="18" t="n">
         <f aca="false">G162+0*G154</f>
-        <v>5.59521299856242</v>
+        <v>5.59521299856243</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43007,15 +43007,15 @@
       </c>
       <c r="E164" s="18" t="n">
         <f aca="false">E160-E163</f>
-        <v>9.49453653171896</v>
+        <v>9.49453653171898</v>
       </c>
       <c r="F164" s="18" t="n">
         <f aca="false">F160-F163</f>
-        <v>7.71485428493344</v>
+        <v>7.71485428493345</v>
       </c>
       <c r="G164" s="18" t="n">
         <f aca="false">G160-G163</f>
-        <v>8.63174212751577</v>
+        <v>8.63174212751578</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="E168" s="18" t="n">
         <f aca="false">(E164+E166)*E167</f>
-        <v>7.02595703347203</v>
+        <v>7.02595703347204</v>
       </c>
       <c r="F168" s="18" t="n">
         <f aca="false">(F164+F166)*F167</f>
@@ -43127,7 +43127,7 @@
       </c>
       <c r="G168" s="18" t="n">
         <f aca="false">(G164+G166)*G167</f>
-        <v>6.38748917436167</v>
+        <v>6.38748917436168</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43175,15 +43175,15 @@
       </c>
       <c r="E170" s="19" t="n">
         <f aca="false">E168/E169</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="F170" s="19" t="n">
         <f aca="false">F168/F169</f>
-        <v>61.3363362449752</v>
+        <v>61.3363362449753</v>
       </c>
       <c r="G170" s="19" t="n">
         <f aca="false">G168/G169</f>
-        <v>68.625980214193</v>
+        <v>68.6259802141931</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43199,7 +43199,7 @@
       </c>
       <c r="E171" s="13" t="n">
         <f aca="false">E170/D170-1</f>
-        <v>0.426926025062102</v>
+        <v>0.426926025062105</v>
       </c>
       <c r="F171" s="13" t="n">
         <f aca="false">F170/E170-1</f>
@@ -43272,11 +43272,11 @@
       </c>
       <c r="E177" s="18" t="n">
         <f aca="false">E78</f>
-        <v>76.4908399924033</v>
+        <v>76.4908399924034</v>
       </c>
       <c r="F177" s="18" t="n">
         <f aca="false">F78</f>
-        <v>108.647210224341</v>
+        <v>108.647210224342</v>
       </c>
       <c r="G177" s="18" t="n">
         <f aca="false">G78</f>
@@ -43288,11 +43288,11 @@
       </c>
       <c r="I177" s="21" t="n">
         <f aca="false">H177*(1+I178)</f>
-        <v>144.105237916415</v>
+        <v>144.105237916416</v>
       </c>
       <c r="J177" s="21" t="n">
         <f aca="false">I177*(1+J178)</f>
-        <v>152.7515521914</v>
+        <v>152.751552191401</v>
       </c>
       <c r="K177" s="7" t="s">
         <v>484</v>
@@ -43324,11 +43324,11 @@
       </c>
       <c r="H178" s="22" t="n">
         <f aca="false">$G$178+($C$184-$G$178)*1/3</f>
-        <v>0.0988344663988053</v>
+        <v>0.0988344663988054</v>
       </c>
       <c r="I178" s="22" t="n">
         <f aca="false">$G$178+($C$184-$G$178)*2/3</f>
-        <v>0.0794172331994026</v>
+        <v>0.0794172331994027</v>
       </c>
       <c r="J178" s="22" t="n">
         <f aca="false">$G$178+($C$184-$G$178)*3/3</f>
@@ -43356,7 +43356,7 @@
       </c>
       <c r="F179" s="18" t="n">
         <f aca="false">F92</f>
-        <v>17.5442617511424</v>
+        <v>17.5442617511425</v>
       </c>
       <c r="G179" s="18" t="n">
         <f aca="false">G92</f>
@@ -43364,7 +43364,7 @@
       </c>
       <c r="H179" s="21" t="n">
         <f aca="false">H177*H180</f>
-        <v>21.949503261858</v>
+        <v>21.9495032618581</v>
       </c>
       <c r="I179" s="21" t="n">
         <f aca="false">I177*I180</f>
@@ -43372,7 +43372,7 @@
       </c>
       <c r="J179" s="21" t="n">
         <f aca="false">J177*J180</f>
-        <v>25.114232405877</v>
+        <v>25.1142324058771</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43483,7 +43483,7 @@
       </c>
       <c r="G182" s="14" t="n">
         <f aca="false">G94</f>
-        <v>214.610421061672</v>
+        <v>214.610421061673</v>
       </c>
       <c r="H182" s="24" t="n">
         <f aca="false">H179/H181</f>
@@ -43524,11 +43524,11 @@
       </c>
       <c r="H183" s="22" t="n">
         <f aca="false">H182/G182-1</f>
-        <v>0.0988344663988052</v>
+        <v>0.0988344663988057</v>
       </c>
       <c r="I183" s="22" t="n">
         <f aca="false">I182/H182-1</f>
-        <v>0.0794172331994028</v>
+        <v>0.0794172331994025</v>
       </c>
       <c r="J183" s="22" t="n">
         <f aca="false">J182/I182-1</f>
@@ -43622,19 +43622,19 @@
       </c>
       <c r="E189" s="18" t="n">
         <f aca="false">E116</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F189" s="18" t="n">
         <f aca="false">F116</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G189" s="18" t="n">
         <f aca="false">G116</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
       <c r="H189" s="21" t="n">
         <f aca="false">G189*(1+H190)</f>
-        <v>94.554417161004</v>
+        <v>94.5544171610041</v>
       </c>
       <c r="I189" s="21" t="n">
         <f aca="false">H189*(1+I190)</f>
@@ -43662,7 +43662,7 @@
       </c>
       <c r="E190" s="13" t="n">
         <f aca="false">E189/D189-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F190" s="13" t="n">
         <f aca="false">F189/E189-1</f>
@@ -43702,7 +43702,7 @@
       </c>
       <c r="E191" s="18" t="n">
         <f aca="false">E130</f>
-        <v>9.46076550392361</v>
+        <v>9.46076550392362</v>
       </c>
       <c r="F191" s="18" t="n">
         <f aca="false">F130</f>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="E192" s="13" t="n">
         <f aca="false">E191/E189</f>
-        <v>0.147691735161201</v>
+        <v>0.147691735161202</v>
       </c>
       <c r="F192" s="13" t="n">
         <f aca="false">F191/F189</f>
@@ -43762,7 +43762,7 @@
       </c>
       <c r="J192" s="22" t="n">
         <f aca="false">$G$192+($C$197-$G$192)*3/3</f>
-        <v>0.120891168068091</v>
+        <v>0.120891168068092</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43862,11 +43862,11 @@
       </c>
       <c r="E195" s="13" t="n">
         <f aca="false">E194/D194-1</f>
-        <v>0.92141973687635</v>
+        <v>0.921419736876353</v>
       </c>
       <c r="F195" s="13" t="n">
         <f aca="false">F194/E194-1</f>
-        <v>0.159406685035449</v>
+        <v>0.159406685035448</v>
       </c>
       <c r="G195" s="13" t="n">
         <f aca="false">G194/F194-1</f>
@@ -43878,11 +43878,11 @@
       </c>
       <c r="I195" s="22" t="n">
         <f aca="false">I194/H194-1</f>
-        <v>-0.00694381735014027</v>
+        <v>-0.00694381735014049</v>
       </c>
       <c r="J195" s="22" t="n">
         <f aca="false">J194/I194-1</f>
-        <v>-0.0526495119399055</v>
+        <v>-0.0526495119399054</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43909,7 +43909,7 @@
       </c>
       <c r="C197" s="13" t="n">
         <f aca="false">(G192+nim10)/2</f>
-        <v>0.120891168068091</v>
+        <v>0.120891168068092</v>
       </c>
       <c r="K197" s="3" t="s">
         <v>496</v>
@@ -43972,7 +43972,7 @@
       </c>
       <c r="E201" s="18" t="n">
         <f aca="false">E154</f>
-        <v>50.0700238577904</v>
+        <v>50.0700238577905</v>
       </c>
       <c r="F201" s="18" t="n">
         <f aca="false">F154</f>
@@ -43980,19 +43980,19 @@
       </c>
       <c r="G201" s="18" t="n">
         <f aca="false">G154</f>
-        <v>48.1830905667014</v>
+        <v>48.1830905667015</v>
       </c>
       <c r="H201" s="21" t="n">
         <f aca="false">G201*(1+H202)</f>
-        <v>51.3270086345337</v>
+        <v>51.3270086345338</v>
       </c>
       <c r="I201" s="21" t="n">
         <f aca="false">H201*(1+I202)</f>
-        <v>53.5148071489643</v>
+        <v>53.5148071489644</v>
       </c>
       <c r="J201" s="21" t="n">
         <f aca="false">I201*(1+J202)</f>
-        <v>54.5851032919436</v>
+        <v>54.5851032919437</v>
       </c>
       <c r="K201" s="7" t="s">
         <v>484</v>
@@ -44012,19 +44012,19 @@
       </c>
       <c r="E202" s="13" t="n">
         <f aca="false">E201/D201-1</f>
-        <v>0.310595048068207</v>
+        <v>0.310595048068208</v>
       </c>
       <c r="F202" s="13" t="n">
         <f aca="false">F201/E201-1</f>
-        <v>-0.115417764206357</v>
+        <v>-0.115417764206358</v>
       </c>
       <c r="G202" s="13" t="n">
         <f aca="false">G201/F201-1</f>
-        <v>0.087874109906257</v>
+        <v>0.0878741099062572</v>
       </c>
       <c r="H202" s="22" t="n">
         <f aca="false">$G$202+($C$208-$G$202)*1/3</f>
-        <v>0.0652494066041713</v>
+        <v>0.0652494066041715</v>
       </c>
       <c r="I202" s="22" t="n">
         <f aca="false">$G$202+($C$208-$G$202)*2/3</f>
@@ -44052,7 +44052,7 @@
       </c>
       <c r="E203" s="18" t="n">
         <f aca="false">E168</f>
-        <v>7.02595703347203</v>
+        <v>7.02595703347204</v>
       </c>
       <c r="F203" s="18" t="n">
         <f aca="false">F168</f>
@@ -44060,11 +44060,11 @@
       </c>
       <c r="G203" s="18" t="n">
         <f aca="false">G168</f>
-        <v>6.38748917436167</v>
+        <v>6.38748917436168</v>
       </c>
       <c r="H203" s="21" t="n">
         <f aca="false">H201*H204</f>
-        <v>5.99766841431324</v>
+        <v>5.99766841431325</v>
       </c>
       <c r="I203" s="21" t="n">
         <f aca="false">I201*I204</f>
@@ -44072,7 +44072,7 @@
       </c>
       <c r="J203" s="21" t="n">
         <f aca="false">J201*J204</f>
-        <v>4.66278082342736</v>
+        <v>4.66278082342737</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44092,7 +44092,7 @@
       </c>
       <c r="E204" s="13" t="n">
         <f aca="false">E203/E201</f>
-        <v>0.140322622042826</v>
+        <v>0.140322622042827</v>
       </c>
       <c r="F204" s="13" t="n">
         <f aca="false">F203/F201</f>
@@ -44175,19 +44175,19 @@
       </c>
       <c r="E206" s="14" t="n">
         <f aca="false">E170</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="F206" s="14" t="n">
         <f aca="false">F170</f>
-        <v>61.3363362449752</v>
+        <v>61.3363362449753</v>
       </c>
       <c r="G206" s="14" t="n">
         <f aca="false">G170</f>
-        <v>68.625980214193</v>
+        <v>68.6259802141931</v>
       </c>
       <c r="H206" s="24" t="n">
         <f aca="false">H203/H205</f>
-        <v>64.4378194148695</v>
+        <v>64.4378194148696</v>
       </c>
       <c r="I206" s="24" t="n">
         <f aca="false">I203/I205</f>
@@ -44195,7 +44195,7 @@
       </c>
       <c r="J206" s="24" t="n">
         <f aca="false">J203/J205</f>
-        <v>50.0960386462999</v>
+        <v>50.0960386463</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44212,7 +44212,7 @@
       </c>
       <c r="E207" s="13" t="n">
         <f aca="false">E206/D206-1</f>
-        <v>0.426926025062102</v>
+        <v>0.426926025062105</v>
       </c>
       <c r="F207" s="13" t="n">
         <f aca="false">F206/E206-1</f>
@@ -44224,11 +44224,11 @@
       </c>
       <c r="H207" s="22" t="n">
         <f aca="false">H206/G206-1</f>
-        <v>-0.0610287938511274</v>
+        <v>-0.061028793851127</v>
       </c>
       <c r="I207" s="22" t="n">
         <f aca="false">I206/H206-1</f>
-        <v>-0.0975934103323299</v>
+        <v>-0.0975934103323303</v>
       </c>
       <c r="J207" s="22" t="n">
         <f aca="false">J206/I206-1</f>
@@ -44352,7 +44352,7 @@
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">PL!E206</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44369,7 +44369,7 @@
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">PL!F206</f>
-        <v>61.3363362449752</v>
+        <v>61.3363362449753</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44378,7 +44378,7 @@
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">PL!G182</f>
-        <v>214.610421061672</v>
+        <v>214.610421061673</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">PL!G194</f>
@@ -44386,7 +44386,7 @@
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">PL!G206</f>
-        <v>68.625980214193</v>
+        <v>68.6259802141931</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44403,7 +44403,7 @@
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">PL!H206</f>
-        <v>64.4378194148695</v>
+        <v>64.4378194148696</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44437,7 +44437,7 @@
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">PL!J206</f>
-        <v>50.0960386462999</v>
+        <v>50.0960386463</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44467,11 +44467,11 @@
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">C8*(1-$B$15)</f>
-        <v>84.0742962234017</v>
+        <v>84.0742962234018</v>
       </c>
       <c r="D16" s="14" t="n">
         <f aca="false">D8*(1-$B$15)</f>
-        <v>62.4370610010407</v>
+        <v>62.4370610010408</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44484,11 +44484,11 @@
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">C9*(1-$B$15)</f>
-        <v>97.4763010810625</v>
+        <v>97.4763010810626</v>
       </c>
       <c r="D17" s="14" t="n">
         <f aca="false">D9*(1-$B$15)</f>
-        <v>50.7336852086787</v>
+        <v>50.7336852086788</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44514,7 +44514,7 @@
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">B11*(1-$B$15)</f>
-        <v>195.057053092442</v>
+        <v>195.057053092443</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">C11*(1-$B$15)</f>
@@ -44522,7 +44522,7 @@
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">D11*(1-$B$15)</f>
-        <v>53.2990433708125</v>
+        <v>53.2990433708126</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44531,11 +44531,11 @@
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">B12*(1-$B$15)</f>
-        <v>210.547944565073</v>
+        <v>210.547944565074</v>
       </c>
       <c r="C20" s="14" t="n">
         <f aca="false">C12*(1-$B$15)</f>
-        <v>120.606867243128</v>
+        <v>120.606867243129</v>
       </c>
       <c r="D20" s="14" t="n">
         <f aca="false">D12*(1-$B$15)</f>
@@ -44556,7 +44556,7 @@
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D13*(1-$B$15)</f>
-        <v>41.4363949736465</v>
+        <v>41.4363949736466</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44565,7 +44565,7 @@
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(B16:B21,1/(1+tp_r)^{1;2;3;4;5;6})+B21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>2929.72353776532</v>
+        <v>2929.72353776533</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(C16:C21,1/(1+tp_r)^{1;2;3;4;5;6})+C21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">B22*(1+tp_r)</f>
-        <v>3222.69589154185</v>
+        <v>3222.69589154186</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">C22*(1+tp_r)</f>
@@ -44593,7 +44593,7 @@
       </c>
       <c r="D23" s="17" t="n">
         <f aca="false">D22*(1+tp_r)</f>
-        <v>700.059483037327</v>
+        <v>700.059483037328</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44602,7 +44602,7 @@
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">tp_wA*B23+tp_wB*C23+tp_wC*D23</f>
-        <v>1978.64511707205</v>
+        <v>1978.64511707206</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>523</v>
@@ -44814,7 +44814,7 @@
       </c>
       <c r="B42" s="13" t="n">
         <f aca="false">B39/px-1</f>
-        <v>1.03586299619186</v>
+        <v>1.03586299619187</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>560</v>
@@ -44835,7 +44835,7 @@
       </c>
       <c r="B44" s="13" t="n">
         <f aca="false">B34/cons_feps-1</f>
-        <v>0.6637493747898</v>
+        <v>0.663749374789802</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>563</v>
@@ -44952,7 +44952,7 @@
       </c>
       <c r="C64" s="16" t="n">
         <f aca="false">px/PL!E29</f>
-        <v>13.3799424864196</v>
+        <v>13.3799424864195</v>
       </c>
       <c r="D64" s="16" t="n">
         <f aca="false">px/PL!E43</f>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="B65" s="16" t="n">
         <f aca="false">px/PL!F15</f>
-        <v>7.21515103431223</v>
+        <v>7.21515103431222</v>
       </c>
       <c r="C65" s="16" t="n">
         <f aca="false">px/PL!F29</f>
@@ -44982,15 +44982,15 @@
       </c>
       <c r="B66" s="16" t="n">
         <f aca="false">px/PL!G15</f>
-        <v>6.33706412424948</v>
+        <v>6.33706412424947</v>
       </c>
       <c r="C66" s="16" t="n">
         <f aca="false">px/PL!G29</f>
-        <v>9.61547573222403</v>
+        <v>9.61547573222401</v>
       </c>
       <c r="D66" s="16" t="n">
         <f aca="false">px/PL!G43</f>
-        <v>19.8175675706958</v>
+        <v>19.8175675706957</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44999,7 +44999,7 @@
       </c>
       <c r="B67" s="14" t="n">
         <f aca="false">2/12*PL!D29+10/12*PL!E29</f>
-        <v>93.5207052585776</v>
+        <v>93.5207052585778</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45174,11 +45174,11 @@
       </c>
       <c r="E80" s="25" t="n">
         <f aca="false">C80*D80</f>
-        <v>2491.6998631208</v>
+        <v>2491.69986312081</v>
       </c>
       <c r="F80" s="31" t="n">
         <f aca="false">E80/px-1</f>
-        <v>0.832132252294708</v>
+        <v>0.83213225229471</v>
       </c>
       <c r="G80" s="30" t="n">
         <f aca="false">px/C80</f>
@@ -45207,11 +45207,11 @@
       </c>
       <c r="F81" s="31" t="n">
         <f aca="false">E81/px-1</f>
-        <v>0.491037799321555</v>
+        <v>0.491037799321558</v>
       </c>
       <c r="G81" s="30" t="n">
         <f aca="false">px/C81</f>
-        <v>13.3799424864196</v>
+        <v>13.3799424864195</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45220,11 +45220,11 @@
       </c>
       <c r="B82" s="29" t="n">
         <f aca="false">PL!E43</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="C82" s="29" t="n">
         <f aca="false">B82</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="D82" s="30" t="n">
         <f aca="false">D76</f>
@@ -45236,7 +45236,7 @@
       </c>
       <c r="F82" s="31" t="n">
         <f aca="false">E82/px-1</f>
-        <v>-0.0780771115357657</v>
+        <v>-0.0780771115357642</v>
       </c>
       <c r="G82" s="30" t="n">
         <f aca="false">px/C82</f>
@@ -45271,7 +45271,7 @@
       </c>
       <c r="B86" s="16" t="n">
         <f aca="false">px*A86/PL!F15</f>
-        <v>7.21515103431223</v>
+        <v>7.21515103431222</v>
       </c>
       <c r="C86" s="16" t="n">
         <f aca="false">px*A86/PL!F43</f>
@@ -45292,11 +45292,11 @@
       </c>
       <c r="B87" s="16" t="n">
         <f aca="false">px*A87/PL!F15</f>
-        <v>7.93666613774346</v>
+        <v>7.93666613774345</v>
       </c>
       <c r="C87" s="16" t="n">
         <f aca="false">px*A87/PL!F43</f>
-        <v>24.3901101954481</v>
+        <v>24.390110195448</v>
       </c>
       <c r="D87" s="16" t="n">
         <f aca="false">pe_mid</f>
@@ -45313,11 +45313,11 @@
       </c>
       <c r="B88" s="16" t="n">
         <f aca="false">px*A88/PL!F15</f>
-        <v>8.7303327515178</v>
+        <v>8.73033275151779</v>
       </c>
       <c r="C88" s="16" t="n">
         <f aca="false">px*A88/PL!F43</f>
-        <v>26.8291212149929</v>
+        <v>26.8291212149928</v>
       </c>
       <c r="D88" s="16" t="n">
         <f aca="false">pe_mid</f>
@@ -45334,7 +45334,7 @@
       </c>
       <c r="B89" s="16" t="n">
         <f aca="false">px*A89/PL!F15</f>
-        <v>10.8227265514684</v>
+        <v>10.8227265514683</v>
       </c>
       <c r="C89" s="16" t="n">
         <f aca="false">px*A89/PL!F43</f>
@@ -45355,11 +45355,11 @@
       </c>
       <c r="B90" s="16" t="n">
         <f aca="false">px*A90/PL!F15</f>
-        <v>14.4303020686245</v>
+        <v>14.4303020686244</v>
       </c>
       <c r="C90" s="16" t="n">
         <f aca="false">px*A90/PL!F43</f>
-        <v>44.3456549008147</v>
+        <v>44.3456549008146</v>
       </c>
       <c r="D90" s="16" t="n">
         <f aca="false">pe_mid</f>
@@ -45676,11 +45676,11 @@
       </c>
       <c r="G122" s="13" t="n">
         <f aca="false">F122/px-1</f>
-        <v>0.241410418382508</v>
+        <v>0.24141041838251</v>
       </c>
       <c r="H122" s="14" t="n">
         <f aca="false">px/E122</f>
-        <v>13.3799424864196</v>
+        <v>13.3799424864195</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45707,11 +45707,11 @@
       </c>
       <c r="G123" s="13" t="n">
         <f aca="false">F123/px-1</f>
-        <v>0.491037799321555</v>
+        <v>0.491037799321558</v>
       </c>
       <c r="H123" s="14" t="n">
         <f aca="false">px/E123</f>
-        <v>13.3799424864196</v>
+        <v>13.3799424864195</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45734,15 +45734,15 @@
       </c>
       <c r="F124" s="18" t="n">
         <f aca="false">C124*E124</f>
-        <v>3217.05418716777</v>
+        <v>3217.05418716778</v>
       </c>
       <c r="G124" s="13" t="n">
         <f aca="false">F124/px-1</f>
-        <v>1.3654810199763</v>
+        <v>1.36548101997631</v>
       </c>
       <c r="H124" s="14" t="n">
         <f aca="false">px/E124</f>
-        <v>13.3799424864196</v>
+        <v>13.3799424864195</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46040,27 +46040,27 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">PL!E78</f>
-        <v>76.4908399924033</v>
+        <v>76.4908399924034</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.557858248317786</v>
+        <v>0.557858248317787</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">PL!E116</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>0.304633701681985</v>
+        <v>0.304633701681987</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">PL!E154</f>
-        <v>50.0700238577904</v>
+        <v>50.0700238577905</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>0.0197560867167093</v>
+        <v>0.0197560867167104</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>665</v>
@@ -46076,27 +46076,27 @@
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">PL!E78</f>
-        <v>76.4908399924033</v>
+        <v>76.4908399924034</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>0.515090123844299</v>
+        <v>0.515090123844301</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">PL!E116</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>0.268817390020708</v>
+        <v>0.26881739002071</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">PL!E154</f>
-        <v>50.0700238577904</v>
+        <v>50.0700238577905</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">G11/B11-1</f>
-        <v>-0.00823943553083173</v>
+        <v>-0.00823943553083062</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>668</v>
@@ -46116,7 +46116,7 @@
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">C12/B12-1</f>
-        <v>0.601862719592879</v>
+        <v>0.601862719592881</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">PL!E132</f>
@@ -46124,15 +46124,15 @@
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">E12/B12-1</f>
-        <v>0.303638348839468</v>
+        <v>0.30363834883947</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">PL!E170</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">G12/B12-1</f>
-        <v>-0.0318640682581194</v>
+        <v>-0.0318640682581179</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>665</v>
@@ -46152,7 +46152,7 @@
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">C13/B13-1</f>
-        <v>0.531541830124547</v>
+        <v>0.531541830124549</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">PL!E132</f>
@@ -46160,15 +46160,15 @@
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">E13/B13-1</f>
-        <v>0.246409344684406</v>
+        <v>0.246409344684408</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">PL!E170</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">G13/B13-1</f>
-        <v>-0.0743647014357518</v>
+        <v>-0.0743647014357505</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>668</v>
@@ -46188,7 +46188,7 @@
       </c>
       <c r="D14" s="13" t="n">
         <f aca="false">C14/B14-1</f>
-        <v>0.403339733108503</v>
+        <v>0.403339733108505</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">PL!E132</f>
@@ -46196,15 +46196,15 @@
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">E14/B14-1</f>
-        <v>0.142075079314756</v>
+        <v>0.142075079314758</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">PL!E170</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">G14/B14-1</f>
-        <v>-0.151847656203209</v>
+        <v>-0.151847656203207</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>674</v>
@@ -46224,7 +46224,7 @@
       </c>
       <c r="D15" s="13" t="n">
         <f aca="false">C15/B15-1</f>
-        <v>0.71356584288258</v>
+        <v>0.713565842882583</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">PL!F132</f>
@@ -46232,11 +46232,11 @@
       </c>
       <c r="F15" s="13" t="n">
         <f aca="false">E15/B15-1</f>
-        <v>0.0713411261592978</v>
+        <v>0.0713411261592993</v>
       </c>
       <c r="G15" s="19" t="n">
         <f aca="false">PL!F170</f>
-        <v>61.3363362449752</v>
+        <v>61.3363362449753</v>
       </c>
       <c r="H15" s="13" t="n">
         <f aca="false">G15/B15-1</f>
@@ -46268,7 +46268,7 @@
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">C17-B17</f>
-        <v>0.0859601775439507</v>
+        <v>0.0859601775439509</v>
       </c>
       <c r="E17" s="13" t="n">
         <f aca="false">PL!E118</f>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="F17" s="13" t="n">
         <f aca="false">E17-B17</f>
-        <v>0.0482977700748068</v>
+        <v>0.0482977700748071</v>
       </c>
       <c r="G17" s="13" t="n">
         <f aca="false">PL!E156</f>
@@ -46284,7 +46284,7 @@
       </c>
       <c r="H17" s="13" t="n">
         <f aca="false">G17-B17</f>
-        <v>-0.0164302364583492</v>
+        <v>-0.0164302364583488</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>668</v>
@@ -46296,15 +46296,15 @@
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">PL!D70</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">PL!D108</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="G18" s="13" t="n">
         <f aca="false">PL!D146</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>163</v>
@@ -46319,15 +46319,15 @@
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">avsh_26+PL!D72</f>
-        <v>0.657628417556845</v>
+        <v>0.657628417556846</v>
       </c>
       <c r="E19" s="13" t="n">
         <f aca="false">avsh_26+PL!D110</f>
-        <v>0.657628417556845</v>
+        <v>0.657628417556846</v>
       </c>
       <c r="G19" s="13" t="n">
         <f aca="false">avsh_26+PL!D148</f>
-        <v>0.657628417556845</v>
+        <v>0.657628417556846</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>687</v>
@@ -46475,7 +46475,7 @@
       </c>
       <c r="F26" s="13" t="n">
         <f aca="false">E26-B26</f>
-        <v>0.00841488850374034</v>
+        <v>0.00841488850374039</v>
       </c>
       <c r="G26" s="13" t="n">
         <f aca="false">PL!E161</f>
@@ -46483,7 +46483,7 @@
       </c>
       <c r="H26" s="13" t="n">
         <f aca="false">G26-B26</f>
-        <v>0.00517848817708255</v>
+        <v>0.00517848817708261</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>698</v>
@@ -46534,7 +46534,7 @@
       </c>
       <c r="D29" s="13" t="n">
         <f aca="false">C29/B29-1</f>
-        <v>0.6637493747898</v>
+        <v>0.663749374789802</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>704</v>
@@ -46557,7 +46557,7 @@
       </c>
       <c r="D30" s="13" t="n">
         <f aca="false">C30/B30-1</f>
-        <v>0.817973522535086</v>
+        <v>0.817973522535088</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>665</v>
@@ -46580,7 +46580,7 @@
       </c>
       <c r="D31" s="13" t="n">
         <f aca="false">C31/B31-1</f>
-        <v>1.33677099971754</v>
+        <v>1.33677099971755</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>36</v>
@@ -46678,7 +46678,7 @@
       </c>
       <c r="C4" s="18" t="n">
         <f aca="false">PL!E116</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="D4" s="18" t="n">
         <f aca="false">PL!E111</f>
@@ -46698,11 +46698,11 @@
       </c>
       <c r="H4" s="18" t="n">
         <f aca="false">PL!F116</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="I4" s="18" t="n">
         <f aca="false">PL!F111</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J4" s="13" t="n">
         <f aca="false">PL!F123</f>
@@ -46726,11 +46726,11 @@
       </c>
       <c r="C5" s="18" t="n">
         <f aca="false">E68</f>
-        <v>58.876962569328</v>
+        <v>58.8769625693281</v>
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">E63</f>
-        <v>44.034693557688</v>
+        <v>44.0346935576881</v>
       </c>
       <c r="E5" s="13" t="n">
         <f aca="false">E75</f>
@@ -46738,19 +46738,19 @@
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">E84</f>
-        <v>91.9561178141619</v>
+        <v>91.956117814162</v>
       </c>
       <c r="G5" s="13" t="n">
         <f aca="false">F5/F$4-1</f>
-        <v>-0.0953179649794804</v>
+        <v>-0.0953179649794806</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">F68</f>
-        <v>62.6785269572156</v>
+        <v>62.6785269572157</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">F63</f>
-        <v>48.0903148025316</v>
+        <v>48.0903148025317</v>
       </c>
       <c r="J5" s="13" t="n">
         <f aca="false">F75</f>
@@ -46758,7 +46758,7 @@
       </c>
       <c r="K5" s="14" t="n">
         <f aca="false">F84</f>
-        <v>99.4450181699461</v>
+        <v>99.4450181699463</v>
       </c>
       <c r="L5" s="13" t="n">
         <f aca="false">K5/K$4-1</f>
@@ -46774,11 +46774,11 @@
       </c>
       <c r="C6" s="18" t="n">
         <f aca="false">E106</f>
-        <v>69.2380669358429</v>
+        <v>69.238066935843</v>
       </c>
       <c r="D6" s="18" t="n">
         <f aca="false">E101</f>
-        <v>54.3957979242029</v>
+        <v>54.395797924203</v>
       </c>
       <c r="E6" s="13" t="n">
         <f aca="false">E113</f>
@@ -46790,15 +46790,15 @@
       </c>
       <c r="G6" s="13" t="n">
         <f aca="false">F6/F$4-1</f>
-        <v>0.0953179649794804</v>
+        <v>0.0953179649794798</v>
       </c>
       <c r="H6" s="18" t="n">
         <f aca="false">F106</f>
-        <v>81.9146528782282</v>
+        <v>81.9146528782284</v>
       </c>
       <c r="I6" s="18" t="n">
         <f aca="false">F101</f>
-        <v>67.3264407235442</v>
+        <v>67.3264407235443</v>
       </c>
       <c r="J6" s="13" t="n">
         <f aca="false">F113</f>
@@ -46810,7 +46810,7 @@
       </c>
       <c r="L6" s="13" t="n">
         <f aca="false">K6/K$4-1</f>
-        <v>0.156803067439596</v>
+        <v>0.156803067439595</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46822,11 +46822,11 @@
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">E144</f>
-        <v>52.7001503508288</v>
+        <v>52.7001503508289</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">E139</f>
-        <v>37.8578813391888</v>
+        <v>37.8578813391889</v>
       </c>
       <c r="E7" s="13" t="n">
         <f aca="false">E151</f>
@@ -46834,7 +46834,7 @@
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">E160</f>
-        <v>80.4043681376082</v>
+        <v>80.4043681376084</v>
       </c>
       <c r="G7" s="13" t="n">
         <f aca="false">F7/F$4-1</f>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="K7" s="14" t="n">
         <f aca="false">F160</f>
-        <v>86.4967622357229</v>
+        <v>86.496762235723</v>
       </c>
       <c r="L7" s="13" t="n">
         <f aca="false">K7/K$4-1</f>
@@ -46870,11 +46870,11 @@
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">E182</f>
-        <v>75.4148791543421</v>
+        <v>75.4148791543422</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">E177</f>
-        <v>60.5726101427021</v>
+        <v>60.5726101427022</v>
       </c>
       <c r="E8" s="13" t="n">
         <f aca="false">E189</f>
@@ -46882,7 +46882,7 @@
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">E198</f>
-        <v>122.884995980418</v>
+        <v>122.884995980419</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">F8/F$4-1</f>
@@ -46890,11 +46890,11 @@
       </c>
       <c r="H8" s="18" t="n">
         <f aca="false">F182</f>
-        <v>88.7846978500185</v>
+        <v>88.7846978500186</v>
       </c>
       <c r="I8" s="18" t="n">
         <f aca="false">F177</f>
-        <v>74.1964856953345</v>
+        <v>74.1964856953346</v>
       </c>
       <c r="J8" s="13" t="n">
         <f aca="false">F189</f>
@@ -46918,11 +46918,11 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">E220</f>
-        <v>62.9638426250089</v>
+        <v>62.963842625009</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">E215</f>
-        <v>48.1215736133689</v>
+        <v>48.121573613369</v>
       </c>
       <c r="E9" s="13" t="n">
         <f aca="false">E227</f>
@@ -46930,19 +46930,19 @@
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">E236</f>
-        <v>99.5993184962114</v>
+        <v>99.5993184962115</v>
       </c>
       <c r="G9" s="13" t="n">
         <f aca="false">F9/F$4-1</f>
-        <v>-0.0201226814956678</v>
+        <v>-0.0201226814956685</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">F220</f>
-        <v>72.6737688573496</v>
+        <v>72.6737688573497</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">F215</f>
-        <v>58.0855567026656</v>
+        <v>58.0855567026657</v>
       </c>
       <c r="J9" s="13" t="n">
         <f aca="false">F227</f>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="L9" s="13" t="n">
         <f aca="false">K9/K$4-1</f>
-        <v>0.00685791731327234</v>
+        <v>0.00685791731327168</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46966,11 +46966,11 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">E258</f>
-        <v>62.0384277478287</v>
+        <v>62.0384277478288</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">E253</f>
-        <v>47.1961587361887</v>
+        <v>47.1961587361888</v>
       </c>
       <c r="E10" s="13" t="n">
         <f aca="false">E265</f>
@@ -46978,11 +46978,11 @@
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">E274</f>
-        <v>97.8686262507635</v>
+        <v>97.8686262507636</v>
       </c>
       <c r="G10" s="13" t="n">
         <f aca="false">F10/F$4-1</f>
-        <v>-0.0371495658381563</v>
+        <v>-0.037149565838157</v>
       </c>
       <c r="H10" s="18" t="n">
         <f aca="false">F258</f>
@@ -46990,7 +46990,7 @@
       </c>
       <c r="I10" s="18" t="n">
         <f aca="false">F253</f>
-        <v>54.5748911876693</v>
+        <v>54.5748911876694</v>
       </c>
       <c r="J10" s="13" t="n">
         <f aca="false">F265</f>
@@ -47002,7 +47002,7 @@
       </c>
       <c r="L10" s="13" t="n">
         <f aca="false">K10/K$4-1</f>
-        <v>-0.0507672122280546</v>
+        <v>-0.0507672122280556</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47026,7 +47026,7 @@
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">E312</f>
-        <v>83.2364099937956</v>
+        <v>83.2364099937957</v>
       </c>
       <c r="G11" s="13" t="n">
         <f aca="false">F11/F$4-1</f>
@@ -47034,11 +47034,11 @@
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">F296</f>
-        <v>60.7549143651143</v>
+        <v>60.7549143651144</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">F291</f>
-        <v>46.1667022104303</v>
+        <v>46.1667022104304</v>
       </c>
       <c r="J11" s="13" t="n">
         <f aca="false">F303</f>
@@ -47046,11 +47046,11 @@
       </c>
       <c r="K11" s="14" t="n">
         <f aca="false">F312</f>
-        <v>95.971923356246</v>
+        <v>95.9719233562461</v>
       </c>
       <c r="L11" s="13" t="n">
         <f aca="false">K11/K$4-1</f>
-        <v>-0.185626305937592</v>
+        <v>-0.185626305937593</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47062,11 +47062,11 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">E334</f>
-        <v>73.9005639007746</v>
+        <v>73.9005639007747</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">E329</f>
-        <v>59.0582948891345</v>
+        <v>59.0582948891346</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">E341</f>
@@ -47078,15 +47078,15 @@
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">F12/F$4-1</f>
-        <v>0.181104133461013</v>
+        <v>0.181104133461012</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">F334</f>
-        <v>83.8382654703295</v>
+        <v>83.8382654703296</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">F329</f>
-        <v>69.2500533156455</v>
+        <v>69.2500533156456</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">F341</f>
@@ -47118,7 +47118,7 @@
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">E379</f>
-        <v>0.299058601459448</v>
+        <v>0.299058601459449</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">E388</f>
@@ -47126,15 +47126,15 @@
       </c>
       <c r="G13" s="13" t="n">
         <f aca="false">F13/F$4-1</f>
-        <v>-0.0116237443164552</v>
+        <v>-0.0116237443164553</v>
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">F372</f>
-        <v>70.8925914977019</v>
+        <v>70.892591497702</v>
       </c>
       <c r="I13" s="18" t="n">
         <f aca="false">F367</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J13" s="13" t="n">
         <f aca="false">F379</f>
@@ -47142,11 +47142,11 @@
       </c>
       <c r="K13" s="14" t="n">
         <f aca="false">F388</f>
-        <v>115.717235620475</v>
+        <v>115.717235620476</v>
       </c>
       <c r="L13" s="13" t="n">
         <f aca="false">K13/K$4-1</f>
-        <v>-0.0180766484263291</v>
+        <v>-0.0180766484263289</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47174,15 +47174,15 @@
       </c>
       <c r="G14" s="13" t="n">
         <f aca="false">F14/F$4-1</f>
-        <v>0.00774916287763694</v>
+        <v>0.0077491628776365</v>
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">F410</f>
-        <v>73.3663029996419</v>
+        <v>73.366302999642</v>
       </c>
       <c r="I14" s="18" t="n">
         <f aca="false">F405</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J14" s="13" t="n">
         <f aca="false">F417</f>
@@ -47194,7 +47194,7 @@
       </c>
       <c r="L14" s="13" t="n">
         <f aca="false">K14/K$4-1</f>
-        <v>0.0138260282719889</v>
+        <v>0.0138260282719891</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47222,15 +47222,15 @@
       </c>
       <c r="G15" s="13" t="n">
         <f aca="false">F15/F$4-1</f>
-        <v>-0.0149448141211562</v>
+        <v>-0.0149448141211567</v>
       </c>
       <c r="H15" s="18" t="n">
         <f aca="false">F448</f>
-        <v>70.4952694958459</v>
+        <v>70.495269495846</v>
       </c>
       <c r="I15" s="18" t="n">
         <f aca="false">F443</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J15" s="13" t="n">
         <f aca="false">F455</f>
@@ -47242,7 +47242,7 @@
       </c>
       <c r="L15" s="13" t="n">
         <f aca="false">K15/K$4-1</f>
-        <v>-0.0231885113549991</v>
+        <v>-0.0231885113549992</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47266,19 +47266,19 @@
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">E502</f>
-        <v>102.814921551581</v>
+        <v>102.814921551582</v>
       </c>
       <c r="G16" s="13" t="n">
         <f aca="false">F16/F$4-1</f>
-        <v>0.0115130419896317</v>
+        <v>0.0115130419896312</v>
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">F486</f>
-        <v>73.7551819089585</v>
+        <v>73.7551819089586</v>
       </c>
       <c r="I16" s="18" t="n">
         <f aca="false">F481</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J16" s="13" t="n">
         <f aca="false">F493</f>
@@ -47290,7 +47290,7 @@
       </c>
       <c r="L16" s="13" t="n">
         <f aca="false">K16/K$4-1</f>
-        <v>0.0188162013001683</v>
+        <v>0.018816201300168</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47302,7 +47302,7 @@
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">E524</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">E519</f>
@@ -47314,19 +47314,19 @@
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">E540</f>
-        <v>99.0733402874343</v>
+        <v>99.0733402874344</v>
       </c>
       <c r="G17" s="13" t="n">
         <f aca="false">F17/F$4-1</f>
-        <v>-0.0252973566298935</v>
+        <v>-0.0252973566298942</v>
       </c>
       <c r="H17" s="18" t="n">
         <f aca="false">F524</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="I17" s="18" t="n">
         <f aca="false">F519</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J17" s="13" t="n">
         <f aca="false">F531</f>
@@ -47338,7 +47338,7 @@
       </c>
       <c r="L17" s="13" t="n">
         <f aca="false">K17/K$4-1</f>
-        <v>-0.0290034680204609</v>
+        <v>-0.0290034680204607</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47350,7 +47350,7 @@
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">E562</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">E557</f>
@@ -47366,15 +47366,15 @@
       </c>
       <c r="G18" s="13" t="n">
         <f aca="false">F18/F$4-1</f>
-        <v>0.0252973566298937</v>
+        <v>0.0252973566298933</v>
       </c>
       <c r="H18" s="18" t="n">
         <f aca="false">F562</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="I18" s="18" t="n">
         <f aca="false">F557</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J18" s="13" t="n">
         <f aca="false">F569</f>
@@ -47386,7 +47386,7 @@
       </c>
       <c r="L18" s="13" t="n">
         <f aca="false">K18/K$4-1</f>
-        <v>0.0290034680204603</v>
+        <v>0.0290034680204605</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47398,7 +47398,7 @@
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">E600</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">E595</f>
@@ -47410,7 +47410,7 @@
       </c>
       <c r="F19" s="14" t="n">
         <f aca="false">E616</f>
-        <v>91.4589983927509</v>
+        <v>91.4589983927511</v>
       </c>
       <c r="G19" s="13" t="n">
         <f aca="false">F19/F$4-1</f>
@@ -47418,11 +47418,11 @@
       </c>
       <c r="H19" s="18" t="n">
         <f aca="false">F600</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="I19" s="18" t="n">
         <f aca="false">F595</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J19" s="13" t="n">
         <f aca="false">F607</f>
@@ -47434,7 +47434,7 @@
       </c>
       <c r="L19" s="13" t="n">
         <f aca="false">K19/K$4-1</f>
-        <v>-0.0975477934738123</v>
+        <v>-0.0975477934738125</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47446,7 +47446,7 @@
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">E638</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="D20" s="18" t="n">
         <f aca="false">E633</f>
@@ -47458,19 +47458,19 @@
       </c>
       <c r="F20" s="14" t="n">
         <f aca="false">E654</f>
-        <v>98.8975284898508</v>
+        <v>98.897528489851</v>
       </c>
       <c r="G20" s="13" t="n">
         <f aca="false">F20/F$4-1</f>
-        <v>-0.0270270270270272</v>
+        <v>-0.027027027027027</v>
       </c>
       <c r="H20" s="18" t="n">
         <f aca="false">F638</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="I20" s="18" t="n">
         <f aca="false">F633</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J20" s="13" t="n">
         <f aca="false">F645</f>
@@ -47482,7 +47482,7 @@
       </c>
       <c r="L20" s="13" t="n">
         <f aca="false">K20/K$4-1</f>
-        <v>-0.0270270270270271</v>
+        <v>-0.027027027027027</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47491,7 +47491,7 @@
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">E676</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">E671</f>
@@ -47503,7 +47503,7 @@
       </c>
       <c r="F21" s="14" t="n">
         <f aca="false">E692</f>
-        <v>107.138989197338</v>
+        <v>107.138989197339</v>
       </c>
       <c r="G21" s="13" t="n">
         <f aca="false">F21/F$4-1</f>
@@ -47511,11 +47511,11 @@
       </c>
       <c r="H21" s="18" t="n">
         <f aca="false">F676</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="I21" s="18" t="n">
         <f aca="false">F671</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="J21" s="13" t="n">
         <f aca="false">F683</f>
@@ -47543,7 +47543,7 @@
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">E709</f>
-        <v>45.1139752625333</v>
+        <v>45.1139752625334</v>
       </c>
       <c r="E22" s="13" t="n">
         <f aca="false">E721</f>
@@ -47551,31 +47551,31 @@
       </c>
       <c r="F22" s="14" t="n">
         <f aca="false">E730</f>
-        <v>97.8747529201851</v>
+        <v>97.8747529201853</v>
       </c>
       <c r="G22" s="13" t="n">
         <f aca="false">F22/F$4-1</f>
-        <v>-0.0370892904819107</v>
+        <v>-0.0370892904819108</v>
       </c>
       <c r="H22" s="18" t="n">
         <f aca="false">F714</f>
-        <v>69.2115156810988</v>
+        <v>69.2115156810989</v>
       </c>
       <c r="I22" s="18" t="n">
         <f aca="false">F709</f>
-        <v>52.8993462827848</v>
+        <v>52.8993462827849</v>
       </c>
       <c r="J22" s="13" t="n">
         <f aca="false">F721</f>
-        <v>0.300872197026807</v>
+        <v>0.300872197026808</v>
       </c>
       <c r="K22" s="14" t="n">
         <f aca="false">F730</f>
-        <v>112.666782962959</v>
+        <v>112.66678296296</v>
       </c>
       <c r="L22" s="13" t="n">
         <f aca="false">K22/K$4-1</f>
-        <v>-0.043961389633843</v>
+        <v>-0.0439613896338426</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47587,11 +47587,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">E752</f>
-        <v>65.4294619383927</v>
+        <v>65.4294619383928</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">E747</f>
-        <v>51.6760080279927</v>
+        <v>51.6760080279928</v>
       </c>
       <c r="E23" s="13" t="n">
         <f aca="false">E759</f>
@@ -47607,11 +47607,11 @@
       </c>
       <c r="H23" s="18" t="n">
         <f aca="false">F752</f>
-        <v>74.1476344596958</v>
+        <v>74.1476344596959</v>
       </c>
       <c r="I23" s="18" t="n">
         <f aca="false">F747</f>
-        <v>60.5937966511898</v>
+        <v>60.5937966511899</v>
       </c>
       <c r="J23" s="13" t="n">
         <f aca="false">F759</f>
@@ -47623,7 +47623,7 @@
       </c>
       <c r="L23" s="13" t="n">
         <f aca="false">K23/K$4-1</f>
-        <v>0.0258958373229612</v>
+        <v>0.025895837322961</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47635,11 +47635,11 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">PL!E78</f>
-        <v>76.4908399924033</v>
+        <v>76.4908399924034</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">PL!E73</f>
-        <v>61.6485709807633</v>
+        <v>61.6485709807634</v>
       </c>
       <c r="E24" s="13" t="n">
         <f aca="false">PL!E85</f>
@@ -47651,15 +47651,15 @@
       </c>
       <c r="G24" s="13" t="n">
         <f aca="false">F24/F$4-1</f>
-        <v>0.228763115950753</v>
+        <v>0.228763115950752</v>
       </c>
       <c r="H24" s="18" t="n">
         <f aca="false">PL!F78</f>
-        <v>108.647210224341</v>
+        <v>108.647210224342</v>
       </c>
       <c r="I24" s="18" t="n">
         <f aca="false">PL!F73</f>
-        <v>94.0589980696574</v>
+        <v>94.0589980696575</v>
       </c>
       <c r="J24" s="13" t="n">
         <f aca="false">PL!F85</f>
@@ -47683,11 +47683,11 @@
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">PL!E154</f>
-        <v>50.0700238577904</v>
+        <v>50.0700238577905</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">PL!E149</f>
-        <v>35.2277548461504</v>
+        <v>35.2277548461505</v>
       </c>
       <c r="E25" s="13" t="n">
         <f aca="false">PL!E161</f>
@@ -47695,7 +47695,7 @@
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">PL!E170</f>
-        <v>75.4855585979144</v>
+        <v>75.4855585979146</v>
       </c>
       <c r="G25" s="13" t="n">
         <f aca="false">F25/F$4-1</f>
@@ -47715,7 +47715,7 @@
       </c>
       <c r="K25" s="14" t="n">
         <f aca="false">PL!F170</f>
-        <v>61.3363362449752</v>
+        <v>61.3363362449753</v>
       </c>
       <c r="L25" s="13" t="n">
         <f aca="false">K25/K$4-1</f>
@@ -47761,7 +47761,7 @@
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1978.64511707205</v>
+        <v>1978.64511707206</v>
       </c>
       <c r="D31" s="17" t="n">
         <f aca="false">Val!B35</f>
@@ -47797,7 +47797,7 @@
       </c>
       <c r="F32" s="13" t="n">
         <f aca="false">E32/E$31-1</f>
-        <v>-0.0487069792893526</v>
+        <v>-0.0487069792893528</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47817,11 +47817,11 @@
       </c>
       <c r="E33" s="17" t="n">
         <f aca="false">tp_w_dcf*C33+(1-tp_w_dcf)*D33</f>
-        <v>2957.52006950183</v>
+        <v>2957.52006950184</v>
       </c>
       <c r="F33" s="13" t="n">
         <f aca="false">E33/E$31-1</f>
-        <v>0.0681696725150724</v>
+        <v>0.0681696725150727</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47865,11 +47865,11 @@
       </c>
       <c r="E35" s="17" t="n">
         <f aca="false">tp_w_dcf*C35+(1-tp_w_dcf)*D35</f>
-        <v>2707.20748862504</v>
+        <v>2707.20748862505</v>
       </c>
       <c r="F35" s="13" t="n">
         <f aca="false">E35/E$31-1</f>
-        <v>-0.0222359042040065</v>
+        <v>-0.0222359042040067</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47878,7 +47878,7 @@
       </c>
       <c r="C36" s="17" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1978.64511707205</v>
+        <v>1978.64511707206</v>
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">Val!B35</f>
@@ -47899,7 +47899,7 @@
       </c>
       <c r="C37" s="17" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1978.64511707205</v>
+        <v>1978.64511707206</v>
       </c>
       <c r="D37" s="17" t="n">
         <f aca="false">Val!B35</f>
@@ -47907,7 +47907,7 @@
       </c>
       <c r="E37" s="17" t="n">
         <f aca="false">0.7*C37+(1-0.7)*D37</f>
-        <v>2452.72225172138</v>
+        <v>2452.72225172139</v>
       </c>
       <c r="F37" s="13" t="n">
         <f aca="false">E37/E$31-1</f>
@@ -47959,7 +47959,7 @@
       </c>
       <c r="D53" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E53" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48082,7 +48082,7 @@
       </c>
       <c r="D58" s="19" t="n">
         <f aca="false">D55*D56*D57/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E58" s="19" t="n">
         <f aca="false">E55*E56*E57/1000</f>
@@ -48130,7 +48130,7 @@
       </c>
       <c r="D60" s="13" t="n">
         <f aca="false">a26_lc/D59</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>461</v>
@@ -48169,7 +48169,7 @@
       </c>
       <c r="D62" s="13" t="n">
         <f aca="false">$D$60*D61</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E62" s="13" t="n">
         <f aca="false">$D$60*E61</f>
@@ -48201,15 +48201,15 @@
       </c>
       <c r="E63" s="18" t="n">
         <f aca="false">E59*E62</f>
-        <v>44.034693557688</v>
+        <v>44.0346935576881</v>
       </c>
       <c r="F63" s="18" t="n">
         <f aca="false">F59*F62</f>
-        <v>48.0903148025316</v>
+        <v>48.0903148025317</v>
       </c>
       <c r="G63" s="18" t="n">
         <f aca="false">G59*G62</f>
-        <v>57.5215951244135</v>
+        <v>57.5215951244136</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48318,15 +48318,15 @@
       </c>
       <c r="E68" s="18" t="n">
         <f aca="false">E63+E65+E66+E67</f>
-        <v>58.876962569328</v>
+        <v>58.8769625693281</v>
       </c>
       <c r="F68" s="18" t="n">
         <f aca="false">F63+F65+F66+F67</f>
-        <v>62.6785269572156</v>
+        <v>62.6785269572157</v>
       </c>
       <c r="G68" s="18" t="n">
         <f aca="false">G63+G65+G66+G67</f>
-        <v>71.8684532649893</v>
+        <v>71.8684532649894</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48342,11 +48342,11 @@
       </c>
       <c r="E69" s="13" t="n">
         <f aca="false">E68/D68-1</f>
-        <v>0.541118810085258</v>
+        <v>0.54111881008526</v>
       </c>
       <c r="F69" s="13" t="n">
         <f aca="false">F68/E68-1</f>
-        <v>0.0645679434194857</v>
+        <v>0.0645679434194859</v>
       </c>
       <c r="G69" s="13" t="n">
         <f aca="false">G68/F68-1</f>
@@ -48402,7 +48402,7 @@
       </c>
       <c r="G71" s="17" t="n">
         <f aca="false">G63/fx/G55*1000</f>
-        <v>35.1648494848773</v>
+        <v>35.1648494848774</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48442,7 +48442,7 @@
       </c>
       <c r="E74" s="18" t="n">
         <f aca="false">$D$73*E68+d_lc*E63</f>
-        <v>17.5189583397815</v>
+        <v>17.5189583397816</v>
       </c>
       <c r="F74" s="18" t="n">
         <f aca="false">$D$73*F68+d_lc*F63</f>
@@ -48502,11 +48502,11 @@
       </c>
       <c r="F76" s="18" t="n">
         <f aca="false">E76*(1+MAX(0,phi*F69))</f>
-        <v>6.20259542916583</v>
+        <v>6.20259542916584</v>
       </c>
       <c r="G76" s="18" t="n">
         <f aca="false">F76*(1+MAX(0,phi*G69))</f>
-        <v>6.79372142543279</v>
+        <v>6.7937214254328</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48530,11 +48530,11 @@
       </c>
       <c r="F77" s="18" t="n">
         <f aca="false">F76+0*F68</f>
-        <v>6.20259542916583</v>
+        <v>6.20259542916584</v>
       </c>
       <c r="G77" s="18" t="n">
         <f aca="false">G76+0*G68</f>
-        <v>6.79372142543279</v>
+        <v>6.7937214254328</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48554,7 +48554,7 @@
       </c>
       <c r="E78" s="18" t="n">
         <f aca="false">E74-E77</f>
-        <v>11.5661953904615</v>
+        <v>11.5661953904616</v>
       </c>
       <c r="F78" s="18" t="n">
         <f aca="false">F74-F77</f>
@@ -48666,11 +48666,11 @@
       </c>
       <c r="E82" s="18" t="n">
         <f aca="false">(E78+E80)*E81</f>
-        <v>8.55898458894154</v>
+        <v>8.55898458894155</v>
       </c>
       <c r="F82" s="18" t="n">
         <f aca="false">(F78+F80)*F81</f>
-        <v>9.25602774666611</v>
+        <v>9.25602774666613</v>
       </c>
       <c r="G82" s="18" t="n">
         <f aca="false">(G78+G80)*G81</f>
@@ -48722,11 +48722,11 @@
       </c>
       <c r="E84" s="19" t="n">
         <f aca="false">E82/E83</f>
-        <v>91.9561178141619</v>
+        <v>91.956117814162</v>
       </c>
       <c r="F84" s="19" t="n">
         <f aca="false">F82/F83</f>
-        <v>99.4450181699461</v>
+        <v>99.4450181699463</v>
       </c>
       <c r="G84" s="19" t="n">
         <f aca="false">G82/G83</f>
@@ -48746,7 +48746,7 @@
       </c>
       <c r="E85" s="13" t="n">
         <f aca="false">E84/D84-1</f>
-        <v>0.738273917685888</v>
+        <v>0.73827391768589</v>
       </c>
       <c r="F85" s="13" t="n">
         <f aca="false">F84/E84-1</f>
@@ -48802,7 +48802,7 @@
       </c>
       <c r="D91" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E91" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48925,7 +48925,7 @@
       </c>
       <c r="D96" s="19" t="n">
         <f aca="false">D93*D94*D95/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E96" s="19" t="n">
         <f aca="false">E93*E94*E95/1000</f>
@@ -48973,7 +48973,7 @@
       </c>
       <c r="D98" s="13" t="n">
         <f aca="false">a26_lc/D97</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>461</v>
@@ -49012,7 +49012,7 @@
       </c>
       <c r="D100" s="13" t="n">
         <f aca="false">$D$98*D99</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E100" s="13" t="n">
         <f aca="false">$D$98*E99</f>
@@ -49044,15 +49044,15 @@
       </c>
       <c r="E101" s="18" t="n">
         <f aca="false">E97*E100</f>
-        <v>54.3957979242029</v>
+        <v>54.395797924203</v>
       </c>
       <c r="F101" s="18" t="n">
         <f aca="false">F97*F100</f>
-        <v>67.3264407235442</v>
+        <v>67.3264407235443</v>
       </c>
       <c r="G101" s="18" t="n">
         <f aca="false">G97*G100</f>
-        <v>86.2823926866203</v>
+        <v>86.2823926866204</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49161,11 +49161,11 @@
       </c>
       <c r="E106" s="18" t="n">
         <f aca="false">E101+E103+E104+E105</f>
-        <v>69.2380669358429</v>
+        <v>69.238066935843</v>
       </c>
       <c r="F106" s="18" t="n">
         <f aca="false">F101+F103+F104+F105</f>
-        <v>81.9146528782282</v>
+        <v>81.9146528782284</v>
       </c>
       <c r="G106" s="18" t="n">
         <f aca="false">G101+G103+G104+G105</f>
@@ -49185,7 +49185,7 @@
       </c>
       <c r="E107" s="13" t="n">
         <f aca="false">E106/D106-1</f>
-        <v>0.812323235987673</v>
+        <v>0.812323235987674</v>
       </c>
       <c r="F107" s="13" t="n">
         <f aca="false">F106/E106-1</f>
@@ -49241,11 +49241,11 @@
       </c>
       <c r="F109" s="17" t="n">
         <f aca="false">F101/fx/F93*1000</f>
-        <v>49.8168701035762</v>
+        <v>49.8168701035763</v>
       </c>
       <c r="G109" s="17" t="n">
         <f aca="false">G101/fx/G93*1000</f>
-        <v>52.747274227316</v>
+        <v>52.7472742273161</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49289,11 +49289,11 @@
       </c>
       <c r="F112" s="18" t="n">
         <f aca="false">$D$111*F106+d_lc*F101</f>
-        <v>24.6769502440278</v>
+        <v>24.6769502440279</v>
       </c>
       <c r="G112" s="18" t="n">
         <f aca="false">$D$111*G106+d_lc*G101</f>
-        <v>30.4934718730669</v>
+        <v>30.493471873067</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49341,15 +49341,15 @@
       </c>
       <c r="E114" s="18" t="n">
         <f aca="false">D114*(1+MAX(0,phi*E107))</f>
-        <v>6.72908094988757</v>
+        <v>6.72908094988758</v>
       </c>
       <c r="F114" s="18" t="n">
         <f aca="false">E114*(1+MAX(0,phi*F107))</f>
-        <v>7.52988540453553</v>
+        <v>7.52988540453554</v>
       </c>
       <c r="G114" s="18" t="n">
         <f aca="false">F114*(1+MAX(0,phi*G107))</f>
-        <v>8.6480883443949</v>
+        <v>8.64808834439491</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49369,15 +49369,15 @@
       </c>
       <c r="E115" s="18" t="n">
         <f aca="false">E114+0*E106</f>
-        <v>6.72908094988757</v>
+        <v>6.72908094988758</v>
       </c>
       <c r="F115" s="18" t="n">
         <f aca="false">F114+0*F106</f>
-        <v>7.52988540453553</v>
+        <v>7.52988540453554</v>
       </c>
       <c r="G115" s="18" t="n">
         <f aca="false">G114+0*G106</f>
-        <v>8.6480883443949</v>
+        <v>8.64808834439491</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49405,7 +49405,7 @@
       </c>
       <c r="G116" s="18" t="n">
         <f aca="false">G112-G115</f>
-        <v>21.845383528672</v>
+        <v>21.8453835286721</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49645,7 +49645,7 @@
       </c>
       <c r="D129" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E129" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49768,7 +49768,7 @@
       </c>
       <c r="D134" s="19" t="n">
         <f aca="false">D131*D132*D133/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E134" s="19" t="n">
         <f aca="false">E131*E132*E133/1000</f>
@@ -49816,7 +49816,7 @@
       </c>
       <c r="D136" s="13" t="n">
         <f aca="false">a26_lc/D135</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H136" s="7" t="s">
         <v>461</v>
@@ -49855,7 +49855,7 @@
       </c>
       <c r="D138" s="13" t="n">
         <f aca="false">$D$136*D137</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E138" s="13" t="n">
         <f aca="false">$D$136*E137</f>
@@ -49887,7 +49887,7 @@
       </c>
       <c r="E139" s="18" t="n">
         <f aca="false">E135*E138</f>
-        <v>37.8578813391888</v>
+        <v>37.8578813391889</v>
       </c>
       <c r="F139" s="18" t="n">
         <f aca="false">F135*F138</f>
@@ -49895,7 +49895,7 @@
       </c>
       <c r="G139" s="18" t="n">
         <f aca="false">G135*G138</f>
-        <v>49.8911794446444</v>
+        <v>49.8911794446445</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50004,7 +50004,7 @@
       </c>
       <c r="E144" s="18" t="n">
         <f aca="false">E139+E141+E142+E143</f>
-        <v>52.7001503508288</v>
+        <v>52.7001503508289</v>
       </c>
       <c r="F144" s="18" t="n">
         <f aca="false">F139+F141+F142+F143</f>
@@ -50012,7 +50012,7 @@
       </c>
       <c r="G144" s="18" t="n">
         <f aca="false">G139+G141+G142+G143</f>
-        <v>64.2380375852202</v>
+        <v>64.2380375852203</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50028,11 +50028,11 @@
       </c>
       <c r="E145" s="13" t="n">
         <f aca="false">E144/D144-1</f>
-        <v>0.379439248489589</v>
+        <v>0.37943924848959</v>
       </c>
       <c r="F145" s="13" t="n">
         <f aca="false">F144/E144-1</f>
-        <v>0.0589814566733522</v>
+        <v>0.058981456673352</v>
       </c>
       <c r="G145" s="13" t="n">
         <f aca="false">G144/F144-1</f>
@@ -50060,11 +50060,11 @@
       </c>
       <c r="F146" s="13" t="n">
         <f aca="false">F139/F144</f>
-        <v>0.738602240453453</v>
+        <v>0.738602240453454</v>
       </c>
       <c r="G146" s="13" t="n">
         <f aca="false">G139/G144</f>
-        <v>0.776661014565664</v>
+        <v>0.776661014565665</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50084,11 +50084,11 @@
       </c>
       <c r="F147" s="17" t="n">
         <f aca="false">F139/fx/F131*1000</f>
-        <v>30.5001245532099</v>
+        <v>30.50012455321</v>
       </c>
       <c r="G147" s="17" t="n">
         <f aca="false">G139/fx/G131*1000</f>
-        <v>30.5001245532099</v>
+        <v>30.50012455321</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50136,7 +50136,7 @@
       </c>
       <c r="G150" s="18" t="n">
         <f aca="false">$D$149*G144+d_lc*G139</f>
-        <v>19.2065010690339</v>
+        <v>19.206501069034</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50352,15 +50352,15 @@
       </c>
       <c r="E158" s="18" t="n">
         <f aca="false">(E154+E156)*E157</f>
-        <v>7.48378426723216</v>
+        <v>7.48378426723217</v>
       </c>
       <c r="F158" s="18" t="n">
         <f aca="false">(F154+F156)*F157</f>
-        <v>8.05084503964213</v>
+        <v>8.05084503964214</v>
       </c>
       <c r="G158" s="18" t="n">
         <f aca="false">(G154+G156)*G157</f>
-        <v>9.58034168475091</v>
+        <v>9.58034168475092</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50408,11 +50408,11 @@
       </c>
       <c r="E160" s="19" t="n">
         <f aca="false">E158/E159</f>
-        <v>80.4043681376082</v>
+        <v>80.4043681376084</v>
       </c>
       <c r="F160" s="19" t="n">
         <f aca="false">F158/F159</f>
-        <v>86.4967622357229</v>
+        <v>86.496762235723</v>
       </c>
       <c r="G160" s="19" t="n">
         <f aca="false">G158/G159</f>
@@ -50432,11 +50432,11 @@
       </c>
       <c r="E161" s="13" t="n">
         <f aca="false">E160/D160-1</f>
-        <v>0.519907748651106</v>
+        <v>0.519907748651109</v>
       </c>
       <c r="F161" s="13" t="n">
         <f aca="false">F160/E160-1</f>
-        <v>0.0757719293022463</v>
+        <v>0.0757719293022461</v>
       </c>
       <c r="G161" s="13" t="n">
         <f aca="false">G160/F160-1</f>
@@ -50488,7 +50488,7 @@
       </c>
       <c r="D167" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E167" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -50611,7 +50611,7 @@
       </c>
       <c r="D172" s="19" t="n">
         <f aca="false">D169*D170*D171/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E172" s="19" t="n">
         <f aca="false">E169*E170*E171/1000</f>
@@ -50659,7 +50659,7 @@
       </c>
       <c r="D174" s="13" t="n">
         <f aca="false">a26_lc/D173</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H174" s="7" t="s">
         <v>461</v>
@@ -50698,7 +50698,7 @@
       </c>
       <c r="D176" s="13" t="n">
         <f aca="false">$D$174*D175</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E176" s="13" t="n">
         <f aca="false">$D$174*E175</f>
@@ -50730,15 +50730,15 @@
       </c>
       <c r="E177" s="18" t="n">
         <f aca="false">E173*E176</f>
-        <v>60.5726101427021</v>
+        <v>60.5726101427022</v>
       </c>
       <c r="F177" s="18" t="n">
         <f aca="false">F173*F176</f>
-        <v>74.1964856953345</v>
+        <v>74.1964856953346</v>
       </c>
       <c r="G177" s="18" t="n">
         <f aca="false">G173*G176</f>
-        <v>89.8041230003599</v>
+        <v>89.8041230003601</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50847,11 +50847,11 @@
       </c>
       <c r="E182" s="18" t="n">
         <f aca="false">E177+E179+E180+E181</f>
-        <v>75.4148791543421</v>
+        <v>75.4148791543422</v>
       </c>
       <c r="F182" s="18" t="n">
         <f aca="false">F177+F179+F180+F181</f>
-        <v>88.7846978500185</v>
+        <v>88.7846978500186</v>
       </c>
       <c r="G182" s="18" t="n">
         <f aca="false">G177+G179+G180+G181</f>
@@ -50871,11 +50871,11 @@
       </c>
       <c r="E183" s="13" t="n">
         <f aca="false">E182/D182-1</f>
-        <v>0.974002797583342</v>
+        <v>0.974002797583345</v>
       </c>
       <c r="F183" s="13" t="n">
         <f aca="false">F182/E182-1</f>
-        <v>0.177283565863894</v>
+        <v>0.177283565863893</v>
       </c>
       <c r="G183" s="13" t="n">
         <f aca="false">G182/F182-1</f>
@@ -50927,11 +50927,11 @@
       </c>
       <c r="F185" s="17" t="n">
         <f aca="false">F177/fx/F169*1000</f>
-        <v>54.9002241957779</v>
+        <v>54.900224195778</v>
       </c>
       <c r="G185" s="17" t="n">
         <f aca="false">G177/fx/G169*1000</f>
-        <v>54.9002241957779</v>
+        <v>54.900224195778</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50979,7 +50979,7 @@
       </c>
       <c r="G188" s="18" t="n">
         <f aca="false">$D$187*G182+d_lc*G177</f>
-        <v>31.5857593702314</v>
+        <v>31.5857593702315</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51027,15 +51027,15 @@
       </c>
       <c r="E190" s="18" t="n">
         <f aca="false">D190*(1+MAX(0,phi*E183))</f>
-        <v>7.1918859117644</v>
+        <v>7.19188591176441</v>
       </c>
       <c r="F190" s="18" t="n">
         <f aca="false">E190*(1+MAX(0,phi*F183))</f>
-        <v>8.02063797858493</v>
+        <v>8.02063797858494</v>
       </c>
       <c r="G190" s="18" t="n">
         <f aca="false">F190*(1+MAX(0,phi*G183))</f>
-        <v>8.92294219225321</v>
+        <v>8.92294219225322</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51055,15 +51055,15 @@
       </c>
       <c r="E191" s="18" t="n">
         <f aca="false">E190+0*E182</f>
-        <v>7.1918859117644</v>
+        <v>7.19188591176441</v>
       </c>
       <c r="F191" s="18" t="n">
         <f aca="false">F190+0*F182</f>
-        <v>8.02063797858493</v>
+        <v>8.02063797858494</v>
       </c>
       <c r="G191" s="18" t="n">
         <f aca="false">G190+0*G182</f>
-        <v>8.92294219225321</v>
+        <v>8.92294219225322</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51087,11 +51087,11 @@
       </c>
       <c r="F192" s="18" t="n">
         <f aca="false">F188-F191</f>
-        <v>18.787101269464</v>
+        <v>18.7871012694641</v>
       </c>
       <c r="G192" s="18" t="n">
         <f aca="false">G188-G191</f>
-        <v>22.6628171779782</v>
+        <v>22.6628171779783</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51251,7 +51251,7 @@
       </c>
       <c r="E198" s="19" t="n">
         <f aca="false">E196/E197</f>
-        <v>122.884995980418</v>
+        <v>122.884995980419</v>
       </c>
       <c r="F198" s="19" t="n">
         <f aca="false">F196/F197</f>
@@ -51275,7 +51275,7 @@
       </c>
       <c r="E199" s="13" t="n">
         <f aca="false">E198/D198-1</f>
-        <v>1.32293172510159</v>
+        <v>1.3229317251016</v>
       </c>
       <c r="F199" s="13" t="n">
         <f aca="false">F198/E198-1</f>
@@ -51331,7 +51331,7 @@
       </c>
       <c r="D205" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E205" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -51478,7 +51478,7 @@
       </c>
       <c r="D211" s="18" t="n">
         <f aca="false">D210*fx</f>
-        <v>118.176547705101</v>
+        <v>118.1765477051</v>
       </c>
       <c r="E211" s="18" t="n">
         <f aca="false">E210*fx</f>
@@ -51549,7 +51549,7 @@
       </c>
       <c r="F214" s="13" t="n">
         <f aca="false">$D$212*F213</f>
-        <v>0.174570854084186</v>
+        <v>0.174570854084187</v>
       </c>
       <c r="G214" s="13" t="n">
         <f aca="false">$D$212*G213</f>
@@ -51573,15 +51573,15 @@
       </c>
       <c r="E215" s="18" t="n">
         <f aca="false">E211*E214</f>
-        <v>48.1215736133689</v>
+        <v>48.121573613369</v>
       </c>
       <c r="F215" s="18" t="n">
         <f aca="false">F211*F214</f>
-        <v>58.0855567026656</v>
+        <v>58.0855567026657</v>
       </c>
       <c r="G215" s="18" t="n">
         <f aca="false">G211*G214</f>
-        <v>71.1411262451411</v>
+        <v>71.1411262451412</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51690,15 +51690,15 @@
       </c>
       <c r="E220" s="18" t="n">
         <f aca="false">E215+E217+E218+E219</f>
-        <v>62.9638426250089</v>
+        <v>62.963842625009</v>
       </c>
       <c r="F220" s="18" t="n">
         <f aca="false">F215+F217+F218+F219</f>
-        <v>72.6737688573496</v>
+        <v>72.6737688573497</v>
       </c>
       <c r="G220" s="18" t="n">
         <f aca="false">G215+G217+G218+G219</f>
-        <v>85.4879843857169</v>
+        <v>85.487984385717</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51714,7 +51714,7 @@
       </c>
       <c r="E221" s="13" t="n">
         <f aca="false">E220/D220-1</f>
-        <v>0.648093889191211</v>
+        <v>0.648093889191212</v>
       </c>
       <c r="F221" s="13" t="n">
         <f aca="false">F220/E220-1</f>
@@ -51766,11 +51766,11 @@
       </c>
       <c r="E223" s="17" t="n">
         <f aca="false">E215/fx/E207*1000</f>
-        <v>36.1084263229069</v>
+        <v>36.108426322907</v>
       </c>
       <c r="F223" s="17" t="n">
         <f aca="false">F215/fx/F207*1000</f>
-        <v>42.9792604815167</v>
+        <v>42.9792604815168</v>
       </c>
       <c r="G223" s="17" t="n">
         <f aca="false">G215/fx/G207*1000</f>
@@ -51934,7 +51934,7 @@
       </c>
       <c r="G230" s="18" t="n">
         <f aca="false">G226-G229</f>
-        <v>18.1216804481202</v>
+        <v>18.1216804481203</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52038,7 +52038,7 @@
       </c>
       <c r="E234" s="18" t="n">
         <f aca="false">(E230+E232)*E233</f>
-        <v>9.27038953298295</v>
+        <v>9.27038953298296</v>
       </c>
       <c r="F234" s="18" t="n">
         <f aca="false">(F230+F232)*F233</f>
@@ -52094,7 +52094,7 @@
       </c>
       <c r="E236" s="19" t="n">
         <f aca="false">E234/E235</f>
-        <v>99.5993184962114</v>
+        <v>99.5993184962115</v>
       </c>
       <c r="F236" s="19" t="n">
         <f aca="false">F234/F235</f>
@@ -52118,7 +52118,7 @@
       </c>
       <c r="E237" s="13" t="n">
         <f aca="false">E236/D236-1</f>
-        <v>0.882755619491697</v>
+        <v>0.882755619491699</v>
       </c>
       <c r="F237" s="13" t="n">
         <f aca="false">F236/E236-1</f>
@@ -52126,7 +52126,7 @@
       </c>
       <c r="G237" s="13" t="n">
         <f aca="false">G236/F236-1</f>
-        <v>0.214227095541804</v>
+        <v>0.214227095541805</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52174,7 +52174,7 @@
       </c>
       <c r="D243" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E243" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -52297,7 +52297,7 @@
       </c>
       <c r="D248" s="19" t="n">
         <f aca="false">D245*D246*D247/1000</f>
-        <v>5.33435805613301</v>
+        <v>5.334358056133</v>
       </c>
       <c r="E248" s="19" t="n">
         <f aca="false">E245*E246*E247/1000</f>
@@ -52396,7 +52396,7 @@
       </c>
       <c r="G252" s="13" t="n">
         <f aca="false">$D$250*G251</f>
-        <v>0.114142481516583</v>
+        <v>0.114142481516584</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52416,15 +52416,15 @@
       </c>
       <c r="E253" s="18" t="n">
         <f aca="false">E249*E252</f>
-        <v>47.1961587361887</v>
+        <v>47.1961587361888</v>
       </c>
       <c r="F253" s="18" t="n">
         <f aca="false">F249*F252</f>
-        <v>54.5748911876693</v>
+        <v>54.5748911876694</v>
       </c>
       <c r="G253" s="18" t="n">
         <f aca="false">G249*G252</f>
-        <v>62.3852953226622</v>
+        <v>62.3852953226623</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52533,7 +52533,7 @@
       </c>
       <c r="E258" s="18" t="n">
         <f aca="false">E253+E255+E256+E257</f>
-        <v>62.0384277478287</v>
+        <v>62.0384277478288</v>
       </c>
       <c r="F258" s="18" t="n">
         <f aca="false">F253+F255+F256+F257</f>
@@ -52541,7 +52541,7 @@
       </c>
       <c r="G258" s="18" t="n">
         <f aca="false">G253+G255+G256+G257</f>
-        <v>76.732153463238</v>
+        <v>76.7321534632381</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52557,7 +52557,7 @@
       </c>
       <c r="E259" s="13" t="n">
         <f aca="false">E258/D258-1</f>
-        <v>0.623870929783687</v>
+        <v>0.623870929783689</v>
       </c>
       <c r="F259" s="13" t="n">
         <f aca="false">F258/E258-1</f>
@@ -52565,7 +52565,7 @@
       </c>
       <c r="G259" s="13" t="n">
         <f aca="false">G258/F258-1</f>
-        <v>0.109437687944947</v>
+        <v>0.109437687944948</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52585,7 +52585,7 @@
       </c>
       <c r="E260" s="13" t="n">
         <f aca="false">E253/E258</f>
-        <v>0.760756847804553</v>
+        <v>0.760756847804554</v>
       </c>
       <c r="F260" s="13" t="n">
         <f aca="false">F253/F258</f>
@@ -52593,7 +52593,7 @@
       </c>
       <c r="G260" s="13" t="n">
         <f aca="false">G253/G258</f>
-        <v>0.813026775699064</v>
+        <v>0.813026775699065</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52661,7 +52661,7 @@
       </c>
       <c r="F264" s="18" t="n">
         <f aca="false">$D$263*F258+d_lc*F253</f>
-        <v>20.7219744546637</v>
+        <v>20.7219744546638</v>
       </c>
       <c r="G264" s="18" t="n">
         <f aca="false">$D$263*G258+d_lc*G253</f>
@@ -52713,7 +52713,7 @@
       </c>
       <c r="E266" s="18" t="n">
         <f aca="false">D266*(1+MAX(0,phi*E259))</f>
-        <v>6.18963946744189</v>
+        <v>6.1896394674419</v>
       </c>
       <c r="F266" s="18" t="n">
         <f aca="false">E266*(1+MAX(0,phi*F259))</f>
@@ -52721,7 +52721,7 @@
       </c>
       <c r="G266" s="18" t="n">
         <f aca="false">F266*(1+MAX(0,phi*G259))</f>
-        <v>7.12484726886144</v>
+        <v>7.12484726886145</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52741,7 +52741,7 @@
       </c>
       <c r="E267" s="18" t="n">
         <f aca="false">E266+0*E258</f>
-        <v>6.18963946744189</v>
+        <v>6.1896394674419</v>
       </c>
       <c r="F267" s="18" t="n">
         <f aca="false">F266+0*F258</f>
@@ -52749,7 +52749,7 @@
       </c>
       <c r="G267" s="18" t="n">
         <f aca="false">G266+0*G258</f>
-        <v>7.12484726886144</v>
+        <v>7.12484726886145</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52881,11 +52881,11 @@
       </c>
       <c r="E272" s="18" t="n">
         <f aca="false">(E268+E270)*E271</f>
-        <v>9.10930217295624</v>
+        <v>9.10930217295625</v>
       </c>
       <c r="F272" s="18" t="n">
         <f aca="false">(F268+F270)*F271</f>
-        <v>10.4120155774095</v>
+        <v>10.4120155774096</v>
       </c>
       <c r="G272" s="18" t="n">
         <f aca="false">(G268+G270)*G271</f>
@@ -52937,7 +52937,7 @@
       </c>
       <c r="E274" s="19" t="n">
         <f aca="false">E272/E273</f>
-        <v>97.8686262507635</v>
+        <v>97.8686262507636</v>
       </c>
       <c r="F274" s="19" t="n">
         <f aca="false">F272/F273</f>
@@ -52961,7 +52961,7 @@
       </c>
       <c r="E275" s="13" t="n">
         <f aca="false">E274/D274-1</f>
-        <v>0.850039827858529</v>
+        <v>0.850039827858531</v>
       </c>
       <c r="F275" s="13" t="n">
         <f aca="false">F274/E274-1</f>
@@ -52969,7 +52969,7 @@
       </c>
       <c r="G275" s="13" t="n">
         <f aca="false">G274/F274-1</f>
-        <v>0.134076367511854</v>
+        <v>0.134076367511855</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53017,7 +53017,7 @@
       </c>
       <c r="D281" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E281" s="19" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -53140,7 +53140,7 @@
       </c>
       <c r="D286" s="19" t="n">
         <f aca="false">D283*D284*D285/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E286" s="19" t="n">
         <f aca="false">E283*E284*E285/1000</f>
@@ -53188,7 +53188,7 @@
       </c>
       <c r="D288" s="13" t="n">
         <f aca="false">a26_lc/D287</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H288" s="7" t="s">
         <v>461</v>
@@ -53227,7 +53227,7 @@
       </c>
       <c r="D290" s="13" t="n">
         <f aca="false">$D$288*D289</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E290" s="13" t="n">
         <f aca="false">$D$288*E289</f>
@@ -53263,11 +53263,11 @@
       </c>
       <c r="F291" s="18" t="n">
         <f aca="false">F287*F290</f>
-        <v>46.1667022104303</v>
+        <v>46.1667022104304</v>
       </c>
       <c r="G291" s="18" t="n">
         <f aca="false">G287*G290</f>
-        <v>55.8781209780017</v>
+        <v>55.8781209780018</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53380,11 +53380,11 @@
       </c>
       <c r="F296" s="18" t="n">
         <f aca="false">F291+F293+F294+F295</f>
-        <v>60.7549143651143</v>
+        <v>60.7549143651144</v>
       </c>
       <c r="G296" s="18" t="n">
         <f aca="false">G291+G293+G294+G295</f>
-        <v>70.2249791185775</v>
+        <v>70.2249791185776</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53400,7 +53400,7 @@
       </c>
       <c r="E297" s="13" t="n">
         <f aca="false">E296/D296-1</f>
-        <v>0.419076818429172</v>
+        <v>0.419076818429174</v>
       </c>
       <c r="F297" s="13" t="n">
         <f aca="false">F296/E296-1</f>
@@ -53432,7 +53432,7 @@
       </c>
       <c r="F298" s="13" t="n">
         <f aca="false">F291/F296</f>
-        <v>0.759884244638807</v>
+        <v>0.759884244638808</v>
       </c>
       <c r="G298" s="13" t="n">
         <f aca="false">G291/G296</f>
@@ -53456,11 +53456,11 @@
       </c>
       <c r="F299" s="17" t="n">
         <f aca="false">F291/fx/F283*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G299" s="17" t="n">
         <f aca="false">G291/fx/G283*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53500,7 +53500,7 @@
       </c>
       <c r="E302" s="18" t="n">
         <f aca="false">$D$301*E296+d_lc*E291</f>
-        <v>16.0728546672506</v>
+        <v>16.0728546672507</v>
       </c>
       <c r="F302" s="18" t="n">
         <f aca="false">$D$301*F296+d_lc*F291</f>
@@ -53556,7 +53556,7 @@
       </c>
       <c r="E304" s="18" t="n">
         <f aca="false">D304*(1+MAX(0,phi*E297))</f>
-        <v>5.60341984906457</v>
+        <v>5.60341984906458</v>
       </c>
       <c r="F304" s="18" t="n">
         <f aca="false">E304*(1+MAX(0,phi*F297))</f>
@@ -53564,7 +53564,7 @@
       </c>
       <c r="G304" s="18" t="n">
         <f aca="false">F304*(1+MAX(0,phi*G297))</f>
-        <v>6.65506255271327</v>
+        <v>6.65506255271328</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53584,7 +53584,7 @@
       </c>
       <c r="E305" s="18" t="n">
         <f aca="false">E304+0*E296</f>
-        <v>5.60341984906457</v>
+        <v>5.60341984906458</v>
       </c>
       <c r="F305" s="18" t="n">
         <f aca="false">F304+0*F296</f>
@@ -53592,7 +53592,7 @@
       </c>
       <c r="G305" s="18" t="n">
         <f aca="false">G304+0*G296</f>
-        <v>6.65506255271327</v>
+        <v>6.65506255271328</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53724,11 +53724,11 @@
       </c>
       <c r="E310" s="18" t="n">
         <f aca="false">(E306+E308)*E309</f>
-        <v>7.74738176545768</v>
+        <v>7.74738176545769</v>
       </c>
       <c r="F310" s="18" t="n">
         <f aca="false">(F306+F308)*F309</f>
-        <v>8.9327630668058</v>
+        <v>8.93276306680581</v>
       </c>
       <c r="G310" s="18" t="n">
         <f aca="false">(G306+G308)*G309</f>
@@ -53780,11 +53780,11 @@
       </c>
       <c r="E312" s="19" t="n">
         <f aca="false">E310/E311</f>
-        <v>83.2364099937956</v>
+        <v>83.2364099937957</v>
       </c>
       <c r="F312" s="19" t="n">
         <f aca="false">F310/F311</f>
-        <v>95.971923356246</v>
+        <v>95.9719233562461</v>
       </c>
       <c r="G312" s="19" t="n">
         <f aca="false">G310/G311</f>
@@ -53804,11 +53804,11 @@
       </c>
       <c r="E313" s="13" t="n">
         <f aca="false">E312/D312-1</f>
-        <v>0.573442680414472</v>
+        <v>0.573442680414475</v>
       </c>
       <c r="F313" s="13" t="n">
         <f aca="false">F312/E312-1</f>
-        <v>0.153004116388486</v>
+        <v>0.153004116388485</v>
       </c>
       <c r="G313" s="13" t="n">
         <f aca="false">G312/F312-1</f>
@@ -53860,7 +53860,7 @@
       </c>
       <c r="D319" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E319" s="19" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -53983,7 +53983,7 @@
       </c>
       <c r="D324" s="19" t="n">
         <f aca="false">D321*D322*D323/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E324" s="19" t="n">
         <f aca="false">E321*E322*E323/1000</f>
@@ -54031,7 +54031,7 @@
       </c>
       <c r="D326" s="13" t="n">
         <f aca="false">a26_lc/D325</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H326" s="7" t="s">
         <v>461</v>
@@ -54070,7 +54070,7 @@
       </c>
       <c r="D328" s="13" t="n">
         <f aca="false">$D$326*D327</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E328" s="13" t="n">
         <f aca="false">$D$326*E327</f>
@@ -54102,15 +54102,15 @@
       </c>
       <c r="E329" s="18" t="n">
         <f aca="false">E325*E328</f>
-        <v>59.0582948891345</v>
+        <v>59.0582948891346</v>
       </c>
       <c r="F329" s="18" t="n">
         <f aca="false">F325*F328</f>
-        <v>69.2500533156455</v>
+        <v>69.2500533156456</v>
       </c>
       <c r="G329" s="18" t="n">
         <f aca="false">G325*G328</f>
-        <v>83.8171814670026</v>
+        <v>83.8171814670027</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54219,15 +54219,15 @@
       </c>
       <c r="E334" s="18" t="n">
         <f aca="false">E329+E331+E332+E333</f>
-        <v>73.9005639007746</v>
+        <v>73.9005639007747</v>
       </c>
       <c r="F334" s="18" t="n">
         <f aca="false">F329+F331+F332+F333</f>
-        <v>83.8382654703295</v>
+        <v>83.8382654703296</v>
       </c>
       <c r="G334" s="18" t="n">
         <f aca="false">G329+G331+G332+G333</f>
-        <v>98.1640396075784</v>
+        <v>98.1640396075785</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54243,7 +54243,7 @@
       </c>
       <c r="E335" s="13" t="n">
         <f aca="false">E334/D334-1</f>
-        <v>0.934365227643758</v>
+        <v>0.934365227643761</v>
       </c>
       <c r="F335" s="13" t="n">
         <f aca="false">F334/E334-1</f>
@@ -54299,11 +54299,11 @@
       </c>
       <c r="F337" s="17" t="n">
         <f aca="false">F329/fx/F321*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G337" s="17" t="n">
         <f aca="false">G329/fx/G321*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54347,7 +54347,7 @@
       </c>
       <c r="F340" s="18" t="n">
         <f aca="false">$D$339*F334+d_lc*F329</f>
-        <v>25.2735711651537</v>
+        <v>25.2735711651538</v>
       </c>
       <c r="G340" s="18" t="n">
         <f aca="false">$D$339*G334+d_lc*G329</f>
@@ -54399,15 +54399,15 @@
       </c>
       <c r="E342" s="18" t="n">
         <f aca="false">D342*(1+MAX(0,phi*E335))</f>
-        <v>7.07842405014298</v>
+        <v>7.07842405014299</v>
       </c>
       <c r="F342" s="18" t="n">
         <f aca="false">E342*(1+MAX(0,phi*F335))</f>
-        <v>7.69713546927227</v>
+        <v>7.69713546927228</v>
       </c>
       <c r="G342" s="18" t="n">
         <f aca="false">F342*(1+MAX(0,phi*G335))</f>
-        <v>8.55204134490917</v>
+        <v>8.55204134490918</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54427,15 +54427,15 @@
       </c>
       <c r="E343" s="18" t="n">
         <f aca="false">E342+0*E334</f>
-        <v>7.07842405014298</v>
+        <v>7.07842405014299</v>
       </c>
       <c r="F343" s="18" t="n">
         <f aca="false">F342+0*F334</f>
-        <v>7.69713546927227</v>
+        <v>7.69713546927228</v>
       </c>
       <c r="G343" s="18" t="n">
         <f aca="false">G342+0*G334</f>
-        <v>8.55204134490917</v>
+        <v>8.55204134490918</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54463,7 +54463,7 @@
       </c>
       <c r="G344" s="18" t="n">
         <f aca="false">G340-G343</f>
-        <v>21.1768292801426</v>
+        <v>21.1768292801427</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54487,7 +54487,7 @@
       </c>
       <c r="F345" s="13" t="n">
         <f aca="false">F344/F334</f>
-        <v>0.209646938629733</v>
+        <v>0.209646938629734</v>
       </c>
       <c r="G345" s="13" t="n">
         <f aca="false">G344/G334</f>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="G348" s="18" t="n">
         <f aca="false">(G344+G346)*G347</f>
-        <v>15.6708536673055</v>
+        <v>15.6708536673056</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54631,7 +54631,7 @@
       </c>
       <c r="G350" s="19" t="n">
         <f aca="false">G348/G349</f>
-        <v>168.364699235595</v>
+        <v>168.364699235596</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54703,7 +54703,7 @@
       </c>
       <c r="D357" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E357" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -54826,7 +54826,7 @@
       </c>
       <c r="D362" s="19" t="n">
         <f aca="false">D359*D360*D361/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E362" s="19" t="n">
         <f aca="false">E359*E360*E361/1000</f>
@@ -54874,7 +54874,7 @@
       </c>
       <c r="D364" s="13" t="n">
         <f aca="false">a26_lc/D363</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H364" s="7" t="s">
         <v>461</v>
@@ -54913,7 +54913,7 @@
       </c>
       <c r="D366" s="13" t="n">
         <f aca="false">$D$364*D365</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E366" s="13" t="n">
         <f aca="false">$D$364*E365</f>
@@ -54949,11 +54949,11 @@
       </c>
       <c r="F367" s="18" t="n">
         <f aca="false">F363*F366</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G367" s="18" t="n">
         <f aca="false">G363*G366</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55066,11 +55066,11 @@
       </c>
       <c r="F372" s="18" t="n">
         <f aca="false">F367+F369+F370+F371</f>
-        <v>70.8925914977019</v>
+        <v>70.892591497702</v>
       </c>
       <c r="G372" s="18" t="n">
         <f aca="false">G367+G369+G370+G371</f>
-        <v>82.3472485847373</v>
+        <v>82.3472485847375</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55086,7 +55086,7 @@
       </c>
       <c r="E373" s="13" t="n">
         <f aca="false">E372/D372-1</f>
-        <v>0.655721023036465</v>
+        <v>0.655721023036467</v>
       </c>
       <c r="F373" s="13" t="n">
         <f aca="false">F372/E372-1</f>
@@ -55114,7 +55114,7 @@
       </c>
       <c r="E374" s="13" t="n">
         <f aca="false">E367/E372</f>
-        <v>0.778042318188342</v>
+        <v>0.778042318188343</v>
       </c>
       <c r="F374" s="13" t="n">
         <f aca="false">F367/F372</f>
@@ -55142,11 +55142,11 @@
       </c>
       <c r="F375" s="17" t="n">
         <f aca="false">F367/fx/F359*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G375" s="17" t="n">
         <f aca="false">G367/fx/G359*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55214,7 +55214,7 @@
       </c>
       <c r="E379" s="13" t="n">
         <f aca="false">E378/E372</f>
-        <v>0.299058601459448</v>
+        <v>0.299058601459449</v>
       </c>
       <c r="F379" s="13" t="n">
         <f aca="false">F378/F372</f>
@@ -55246,11 +55246,11 @@
       </c>
       <c r="F380" s="18" t="n">
         <f aca="false">E380*(1+MAX(0,phi*F373))</f>
-        <v>6.77372921137998</v>
+        <v>6.77372921137999</v>
       </c>
       <c r="G380" s="18" t="n">
         <f aca="false">F380*(1+MAX(0,phi*G373))</f>
-        <v>7.48514324478501</v>
+        <v>7.48514324478502</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55274,11 +55274,11 @@
       </c>
       <c r="F381" s="18" t="n">
         <f aca="false">F380+0*F372</f>
-        <v>6.77372921137998</v>
+        <v>6.77372921137999</v>
       </c>
       <c r="G381" s="18" t="n">
         <f aca="false">G380+0*G372</f>
-        <v>7.48514324478501</v>
+        <v>7.48514324478502</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55410,7 +55410,7 @@
       </c>
       <c r="E386" s="18" t="n">
         <f aca="false">(E382+E384)*E385</f>
-        <v>9.35079598466806</v>
+        <v>9.35079598466808</v>
       </c>
       <c r="F386" s="18" t="n">
         <f aca="false">(F382+F384)*F385</f>
@@ -55470,11 +55470,11 @@
       </c>
       <c r="F388" s="19" t="n">
         <f aca="false">F386/F387</f>
-        <v>115.717235620475</v>
+        <v>115.717235620476</v>
       </c>
       <c r="G388" s="19" t="n">
         <f aca="false">G386/G387</f>
-        <v>138.579091123568</v>
+        <v>138.579091123569</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55490,7 +55490,7 @@
       </c>
       <c r="E389" s="13" t="n">
         <f aca="false">E388/D388-1</f>
-        <v>0.899085645130309</v>
+        <v>0.899085645130312</v>
       </c>
       <c r="F389" s="13" t="n">
         <f aca="false">F388/E388-1</f>
@@ -55546,7 +55546,7 @@
       </c>
       <c r="D395" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E395" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55669,7 +55669,7 @@
       </c>
       <c r="D400" s="19" t="n">
         <f aca="false">D397*D398*D399/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E400" s="19" t="n">
         <f aca="false">E397*E398*E399/1000</f>
@@ -55717,7 +55717,7 @@
       </c>
       <c r="D402" s="13" t="n">
         <f aca="false">a26_lc/D401</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H402" s="7" t="s">
         <v>461</v>
@@ -55756,7 +55756,7 @@
       </c>
       <c r="D404" s="13" t="n">
         <f aca="false">$D$402*D403</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E404" s="13" t="n">
         <f aca="false">$D$402*E403</f>
@@ -55792,11 +55792,11 @@
       </c>
       <c r="F405" s="18" t="n">
         <f aca="false">F401*F404</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G405" s="18" t="n">
         <f aca="false">G401*G404</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55909,11 +55909,11 @@
       </c>
       <c r="F410" s="18" t="n">
         <f aca="false">F405+F407+F408+F409</f>
-        <v>73.3663029996419</v>
+        <v>73.366302999642</v>
       </c>
       <c r="G410" s="18" t="n">
         <f aca="false">G405+G407+G408+G409</f>
-        <v>85.8004161273104</v>
+        <v>85.8004161273105</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55929,7 +55929,7 @@
       </c>
       <c r="E411" s="13" t="n">
         <f aca="false">E410/D410-1</f>
-        <v>0.690721023036465</v>
+        <v>0.690721023036467</v>
       </c>
       <c r="F411" s="13" t="n">
         <f aca="false">F410/E410-1</f>
@@ -55961,7 +55961,7 @@
       </c>
       <c r="F412" s="13" t="n">
         <f aca="false">F405/F410</f>
-        <v>0.78657878894783</v>
+        <v>0.786578788947831</v>
       </c>
       <c r="G412" s="13" t="n">
         <f aca="false">G405/G410</f>
@@ -55985,11 +55985,11 @@
       </c>
       <c r="F413" s="17" t="n">
         <f aca="false">F405/fx/F397*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G413" s="17" t="n">
         <f aca="false">G405/fx/G397*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56089,11 +56089,11 @@
       </c>
       <c r="F418" s="18" t="n">
         <f aca="false">E418*(1+MAX(0,phi*F411))</f>
-        <v>6.94439418637151</v>
+        <v>6.94439418637152</v>
       </c>
       <c r="G418" s="18" t="n">
         <f aca="false">F418*(1+MAX(0,phi*G411))</f>
-        <v>7.70940205239383</v>
+        <v>7.70940205239384</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56117,11 +56117,11 @@
       </c>
       <c r="F419" s="18" t="n">
         <f aca="false">F418+0*F410</f>
-        <v>6.94439418637151</v>
+        <v>6.94439418637152</v>
       </c>
       <c r="G419" s="18" t="n">
         <f aca="false">G418+0*G410</f>
-        <v>7.70940205239383</v>
+        <v>7.70940205239384</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56253,7 +56253,7 @@
       </c>
       <c r="E424" s="18" t="n">
         <f aca="false">(E420+E422)*E423</f>
-        <v>9.53407851676064</v>
+        <v>9.53407851676065</v>
       </c>
       <c r="F424" s="18" t="n">
         <f aca="false">(F420+F422)*F423</f>
@@ -56317,7 +56317,7 @@
       </c>
       <c r="G426" s="19" t="n">
         <f aca="false">G424/G425</f>
-        <v>143.938510373805</v>
+        <v>143.938510373806</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56333,7 +56333,7 @@
       </c>
       <c r="E427" s="13" t="n">
         <f aca="false">E426/D426-1</f>
-        <v>0.936309131373711</v>
+        <v>0.936309131373714</v>
       </c>
       <c r="F427" s="13" t="n">
         <f aca="false">F426/E426-1</f>
@@ -56389,7 +56389,7 @@
       </c>
       <c r="D433" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E433" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56512,7 +56512,7 @@
       </c>
       <c r="D438" s="19" t="n">
         <f aca="false">D435*D436*D437/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E438" s="19" t="n">
         <f aca="false">E435*E436*E437/1000</f>
@@ -56560,7 +56560,7 @@
       </c>
       <c r="D440" s="13" t="n">
         <f aca="false">a26_lc/D439</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H440" s="7" t="s">
         <v>461</v>
@@ -56599,7 +56599,7 @@
       </c>
       <c r="D442" s="13" t="n">
         <f aca="false">$D$440*D441</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E442" s="13" t="n">
         <f aca="false">$D$440*E441</f>
@@ -56635,11 +56635,11 @@
       </c>
       <c r="F443" s="18" t="n">
         <f aca="false">F439*F442</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G443" s="18" t="n">
         <f aca="false">G439*G442</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56752,11 +56752,11 @@
       </c>
       <c r="F448" s="18" t="n">
         <f aca="false">F443+F445+F446+F447</f>
-        <v>70.4952694958459</v>
+        <v>70.495269495846</v>
       </c>
       <c r="G448" s="18" t="n">
         <f aca="false">G443+G445+G446+G447</f>
-        <v>81.6921066281193</v>
+        <v>81.6921066281194</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56772,7 +56772,7 @@
       </c>
       <c r="E449" s="13" t="n">
         <f aca="false">E448/D448-1</f>
-        <v>0.649721023036465</v>
+        <v>0.649721023036467</v>
       </c>
       <c r="F449" s="13" t="n">
         <f aca="false">F448/E448-1</f>
@@ -56828,11 +56828,11 @@
       </c>
       <c r="F451" s="17" t="n">
         <f aca="false">F443/fx/F435*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G451" s="17" t="n">
         <f aca="false">G443/fx/G435*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56932,11 +56932,11 @@
       </c>
       <c r="F456" s="18" t="n">
         <f aca="false">E456*(1+MAX(0,phi*F449))</f>
-        <v>6.746135456705</v>
+        <v>6.74613545670501</v>
       </c>
       <c r="G456" s="18" t="n">
         <f aca="false">F456*(1+MAX(0,phi*G449))</f>
-        <v>7.44260767872453</v>
+        <v>7.44260767872454</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56960,11 +56960,11 @@
       </c>
       <c r="F457" s="18" t="n">
         <f aca="false">F456+0*F448</f>
-        <v>6.746135456705</v>
+        <v>6.74613545670501</v>
       </c>
       <c r="G457" s="18" t="n">
         <f aca="false">G456+0*G448</f>
-        <v>7.44260767872453</v>
+        <v>7.44260767872454</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="E458" s="18" t="n">
         <f aca="false">E454-E457</f>
-        <v>12.5937515162481</v>
+        <v>12.5937515162482</v>
       </c>
       <c r="F458" s="18" t="n">
         <f aca="false">F454-F457</f>
@@ -57096,7 +57096,7 @@
       </c>
       <c r="E462" s="18" t="n">
         <f aca="false">(E458+E460)*E461</f>
-        <v>9.31937612202362</v>
+        <v>9.31937612202363</v>
       </c>
       <c r="F462" s="18" t="n">
         <f aca="false">(F458+F460)*F461</f>
@@ -57176,7 +57176,7 @@
       </c>
       <c r="E465" s="13" t="n">
         <f aca="false">E464/D464-1</f>
-        <v>0.892704476060012</v>
+        <v>0.892704476060015</v>
       </c>
       <c r="F465" s="13" t="n">
         <f aca="false">F464/E464-1</f>
@@ -57232,7 +57232,7 @@
       </c>
       <c r="D471" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E471" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57355,7 +57355,7 @@
       </c>
       <c r="D476" s="19" t="n">
         <f aca="false">D473*D474*D475/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E476" s="19" t="n">
         <f aca="false">E473*E474*E475/1000</f>
@@ -57403,7 +57403,7 @@
       </c>
       <c r="D478" s="13" t="n">
         <f aca="false">a26_lc/D477</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H478" s="7" t="s">
         <v>461</v>
@@ -57442,7 +57442,7 @@
       </c>
       <c r="D480" s="13" t="n">
         <f aca="false">$D$478*D479</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E480" s="13" t="n">
         <f aca="false">$D$478*E479</f>
@@ -57478,11 +57478,11 @@
       </c>
       <c r="F481" s="18" t="n">
         <f aca="false">F477*F480</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G481" s="18" t="n">
         <f aca="false">G477*G480</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57595,11 +57595,11 @@
       </c>
       <c r="F486" s="18" t="n">
         <f aca="false">F481+F483+F484+F485</f>
-        <v>73.7551819089585</v>
+        <v>73.7551819089586</v>
       </c>
       <c r="G486" s="18" t="n">
         <f aca="false">G481+G483+G484+G485</f>
-        <v>86.3611394767123</v>
+        <v>86.3611394767125</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57615,7 +57615,7 @@
       </c>
       <c r="E487" s="13" t="n">
         <f aca="false">E486/D486-1</f>
-        <v>0.697521023036465</v>
+        <v>0.697521023036468</v>
       </c>
       <c r="F487" s="13" t="n">
         <f aca="false">F486/E486-1</f>
@@ -57643,7 +57643,7 @@
       </c>
       <c r="E488" s="13" t="n">
         <f aca="false">E481/E486</f>
-        <v>0.758883693076237</v>
+        <v>0.758883693076238</v>
       </c>
       <c r="F488" s="13" t="n">
         <f aca="false">F481/F486</f>
@@ -57671,11 +57671,11 @@
       </c>
       <c r="F489" s="17" t="n">
         <f aca="false">F481/fx/F473*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G489" s="17" t="n">
         <f aca="false">G481/fx/G473*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57775,11 +57775,11 @@
       </c>
       <c r="F494" s="18" t="n">
         <f aca="false">E494*(1+MAX(0,phi*F487))</f>
-        <v>6.9715952012769</v>
+        <v>6.97159520127691</v>
       </c>
       <c r="G494" s="18" t="n">
         <f aca="false">F494*(1+MAX(0,phi*G487))</f>
-        <v>7.74610839693232</v>
+        <v>7.74610839693233</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57803,11 +57803,11 @@
       </c>
       <c r="F495" s="18" t="n">
         <f aca="false">F494+0*F486</f>
-        <v>6.9715952012769</v>
+        <v>6.97159520127691</v>
       </c>
       <c r="G495" s="18" t="n">
         <f aca="false">G494+0*G486</f>
-        <v>7.74610839693232</v>
+        <v>7.74610839693233</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57835,7 +57835,7 @@
       </c>
       <c r="G496" s="18" t="n">
         <f aca="false">G492-G495</f>
-        <v>18.2136846985503</v>
+        <v>18.2136846985504</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57939,11 +57939,11 @@
       </c>
       <c r="E500" s="18" t="n">
         <f aca="false">(E496+E498)*E499</f>
-        <v>9.56968769442434</v>
+        <v>9.56968769442435</v>
       </c>
       <c r="F500" s="18" t="n">
         <f aca="false">(F496+F498)*F499</f>
-        <v>11.1752673265255</v>
+        <v>11.1752673265256</v>
       </c>
       <c r="G500" s="18" t="n">
         <f aca="false">(G496+G498)*G499</f>
@@ -57995,7 +57995,7 @@
       </c>
       <c r="E502" s="19" t="n">
         <f aca="false">E500/E501</f>
-        <v>102.814921551581</v>
+        <v>102.814921551582</v>
       </c>
       <c r="F502" s="19" t="n">
         <f aca="false">F500/F501</f>
@@ -58019,7 +58019,7 @@
       </c>
       <c r="E503" s="13" t="n">
         <f aca="false">E502/D502-1</f>
-        <v>0.943541122986714</v>
+        <v>0.943541122986717</v>
       </c>
       <c r="F503" s="13" t="n">
         <f aca="false">F502/E502-1</f>
@@ -58075,7 +58075,7 @@
       </c>
       <c r="D509" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E509" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58198,7 +58198,7 @@
       </c>
       <c r="D514" s="19" t="n">
         <f aca="false">D511*D512*D513/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E514" s="19" t="n">
         <f aca="false">E511*E512*E513/1000</f>
@@ -58246,7 +58246,7 @@
       </c>
       <c r="D516" s="13" t="n">
         <f aca="false">a26_lc/D515</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H516" s="7" t="s">
         <v>461</v>
@@ -58285,7 +58285,7 @@
       </c>
       <c r="D518" s="13" t="n">
         <f aca="false">$D$516*D517</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E518" s="13" t="n">
         <f aca="false">$D$516*E517</f>
@@ -58321,11 +58321,11 @@
       </c>
       <c r="F519" s="18" t="n">
         <f aca="false">F515*F518</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G519" s="18" t="n">
         <f aca="false">G515*G518</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58434,15 +58434,15 @@
       </c>
       <c r="E524" s="18" t="n">
         <f aca="false">E519+E521+E522+E523</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F524" s="18" t="n">
         <f aca="false">F519+F521+F522+F523</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G524" s="18" t="n">
         <f aca="false">G519+G521+G522+G523</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58458,7 +58458,7 @@
       </c>
       <c r="E525" s="13" t="n">
         <f aca="false">E524/D524-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F525" s="13" t="n">
         <f aca="false">F524/E524-1</f>
@@ -58514,11 +58514,11 @@
       </c>
       <c r="F527" s="17" t="n">
         <f aca="false">F519/fx/F511*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G527" s="17" t="n">
         <f aca="false">G519/fx/G511*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58622,7 +58622,7 @@
       </c>
       <c r="G532" s="18" t="n">
         <f aca="false">F532*(1+MAX(0,phi*G525))</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58650,7 +58650,7 @@
       </c>
       <c r="G533" s="18" t="n">
         <f aca="false">G532+0*G524</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58782,7 +58782,7 @@
       </c>
       <c r="E538" s="18" t="n">
         <f aca="false">(E534+E536)*E537</f>
-        <v>9.22143314497906</v>
+        <v>9.22143314497907</v>
       </c>
       <c r="F538" s="18" t="n">
         <f aca="false">(F534+F536)*F537</f>
@@ -58838,7 +58838,7 @@
       </c>
       <c r="E540" s="19" t="n">
         <f aca="false">E538/E539</f>
-        <v>99.0733402874343</v>
+        <v>99.0733402874344</v>
       </c>
       <c r="F540" s="19" t="n">
         <f aca="false">F538/F539</f>
@@ -58862,15 +58862,15 @@
       </c>
       <c r="E541" s="13" t="n">
         <f aca="false">E540/D540-1</f>
-        <v>0.872812896556873</v>
+        <v>0.872812896556875</v>
       </c>
       <c r="F541" s="13" t="n">
         <f aca="false">F540/E540-1</f>
-        <v>0.154998273556381</v>
+        <v>0.154998273556382</v>
       </c>
       <c r="G541" s="13" t="n">
         <f aca="false">G540/F540-1</f>
-        <v>0.195740093664925</v>
+        <v>0.195740093664924</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="D547" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E547" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59041,7 +59041,7 @@
       </c>
       <c r="D552" s="19" t="n">
         <f aca="false">D549*D550*D551/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E552" s="19" t="n">
         <f aca="false">E549*E550*E551/1000</f>
@@ -59089,7 +59089,7 @@
       </c>
       <c r="D554" s="13" t="n">
         <f aca="false">a26_lc/D553</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H554" s="7" t="s">
         <v>461</v>
@@ -59128,7 +59128,7 @@
       </c>
       <c r="D556" s="13" t="n">
         <f aca="false">$D$554*D555</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E556" s="13" t="n">
         <f aca="false">$D$554*E555</f>
@@ -59164,11 +59164,11 @@
       </c>
       <c r="F557" s="18" t="n">
         <f aca="false">F553*F556</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G557" s="18" t="n">
         <f aca="false">G553*G556</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59277,15 +59277,15 @@
       </c>
       <c r="E562" s="18" t="n">
         <f aca="false">E557+E559+E560+E561</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F562" s="18" t="n">
         <f aca="false">F557+F559+F560+F561</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G562" s="18" t="n">
         <f aca="false">G557+G559+G560+G561</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59301,7 +59301,7 @@
       </c>
       <c r="E563" s="13" t="n">
         <f aca="false">E562/D562-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F563" s="13" t="n">
         <f aca="false">F562/E562-1</f>
@@ -59357,11 +59357,11 @@
       </c>
       <c r="F565" s="17" t="n">
         <f aca="false">F557/fx/F549*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G565" s="17" t="n">
         <f aca="false">G557/fx/G549*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59409,7 +59409,7 @@
       </c>
       <c r="G568" s="18" t="n">
         <f aca="false">$D$567*G562+d_lc_hi*G557</f>
-        <v>25.9760585877723</v>
+        <v>25.9760585877724</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59465,7 +59465,7 @@
       </c>
       <c r="G570" s="18" t="n">
         <f aca="false">F570*(1+MAX(0,phi*G563))</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59493,7 +59493,7 @@
       </c>
       <c r="G571" s="18" t="n">
         <f aca="false">G570+0*G562</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59513,7 +59513,7 @@
       </c>
       <c r="E572" s="18" t="n">
         <f aca="false">E568-E571</f>
-        <v>13.1082403552272</v>
+        <v>13.1082403552273</v>
       </c>
       <c r="F572" s="18" t="n">
         <f aca="false">F568-F571</f>
@@ -59625,7 +59625,7 @@
       </c>
       <c r="E576" s="18" t="n">
         <f aca="false">(E572+E574)*E575</f>
-        <v>9.70009786286816</v>
+        <v>9.70009786286817</v>
       </c>
       <c r="F576" s="18" t="n">
         <f aca="false">(F572+F574)*F575</f>
@@ -59633,7 +59633,7 @@
       </c>
       <c r="G576" s="18" t="n">
         <f aca="false">(G572+G574)*G575</f>
-        <v>13.5938100673642</v>
+        <v>13.5938100673643</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59705,11 +59705,11 @@
       </c>
       <c r="E579" s="13" t="n">
         <f aca="false">E578/D578-1</f>
-        <v>0.970026577195827</v>
+        <v>0.97002657719583</v>
       </c>
       <c r="F579" s="13" t="n">
         <f aca="false">F578/E578-1</f>
-        <v>0.16359755736524</v>
+        <v>0.163597557365241</v>
       </c>
       <c r="G579" s="13" t="n">
         <f aca="false">G578/F578-1</f>
@@ -59761,7 +59761,7 @@
       </c>
       <c r="D585" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E585" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59884,7 +59884,7 @@
       </c>
       <c r="D590" s="19" t="n">
         <f aca="false">D587*D588*D589/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E590" s="19" t="n">
         <f aca="false">E587*E588*E589/1000</f>
@@ -59932,7 +59932,7 @@
       </c>
       <c r="D592" s="13" t="n">
         <f aca="false">a26_lc/D591</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H592" s="7" t="s">
         <v>461</v>
@@ -59971,7 +59971,7 @@
       </c>
       <c r="D594" s="13" t="n">
         <f aca="false">$D$592*D593</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E594" s="13" t="n">
         <f aca="false">$D$592*E593</f>
@@ -60007,11 +60007,11 @@
       </c>
       <c r="F595" s="18" t="n">
         <f aca="false">F591*F594</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G595" s="18" t="n">
         <f aca="false">G591*G594</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60120,15 +60120,15 @@
       </c>
       <c r="E600" s="18" t="n">
         <f aca="false">E595+E597+E598+E599</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F600" s="18" t="n">
         <f aca="false">F595+F597+F598+F599</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G600" s="18" t="n">
         <f aca="false">G595+G597+G598+G599</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60144,7 +60144,7 @@
       </c>
       <c r="E601" s="13" t="n">
         <f aca="false">E600/D600-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F601" s="13" t="n">
         <f aca="false">F600/E600-1</f>
@@ -60200,11 +60200,11 @@
       </c>
       <c r="F603" s="17" t="n">
         <f aca="false">F595/fx/F587*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G603" s="17" t="n">
         <f aca="false">G595/fx/G587*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60308,7 +60308,7 @@
       </c>
       <c r="G608" s="18" t="n">
         <f aca="false">F608*(1+MAX(0,phi*G601))</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60328,15 +60328,15 @@
       </c>
       <c r="E609" s="18" t="n">
         <f aca="false">E608+opx_adj_hi*E600</f>
-        <v>7.62207224465549</v>
+        <v>7.6220722446555</v>
       </c>
       <c r="F609" s="18" t="n">
         <f aca="false">F608+opx_adj_hi*F600</f>
-        <v>8.31697369242595</v>
+        <v>8.31697369242596</v>
       </c>
       <c r="G609" s="18" t="n">
         <f aca="false">G608+opx_adj_hi*G600</f>
-        <v>9.28993517048761</v>
+        <v>9.28993517048762</v>
       </c>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60384,7 +60384,7 @@
       </c>
       <c r="E611" s="13" t="n">
         <f aca="false">E610/E600</f>
-        <v>0.179583425893515</v>
+        <v>0.179583425893516</v>
       </c>
       <c r="F611" s="13" t="n">
         <f aca="false">F610/F600</f>
@@ -60468,11 +60468,11 @@
       </c>
       <c r="E614" s="18" t="n">
         <f aca="false">(E610+E612)*E613</f>
-        <v>8.51271428558534</v>
+        <v>8.51271428558536</v>
       </c>
       <c r="F614" s="18" t="n">
         <f aca="false">(F610+F612)*F613</f>
-        <v>9.89888524001951</v>
+        <v>9.89888524001952</v>
       </c>
       <c r="G614" s="18" t="n">
         <f aca="false">(G610+G612)*G613</f>
@@ -60524,7 +60524,7 @@
       </c>
       <c r="E616" s="19" t="n">
         <f aca="false">E614/E615</f>
-        <v>91.4589983927509</v>
+        <v>91.4589983927511</v>
       </c>
       <c r="F616" s="19" t="n">
         <f aca="false">F614/F615</f>
@@ -60548,11 +60548,11 @@
       </c>
       <c r="E617" s="13" t="n">
         <f aca="false">E616/D616-1</f>
-        <v>0.728876721014753</v>
+        <v>0.728876721014756</v>
       </c>
       <c r="F617" s="13" t="n">
         <f aca="false">F616/E616-1</f>
-        <v>0.162835366950044</v>
+        <v>0.162835366950043</v>
       </c>
       <c r="G617" s="13" t="n">
         <f aca="false">G616/F616-1</f>
@@ -60604,7 +60604,7 @@
       </c>
       <c r="D623" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E623" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -60727,7 +60727,7 @@
       </c>
       <c r="D628" s="19" t="n">
         <f aca="false">D625*D626*D627/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E628" s="19" t="n">
         <f aca="false">E625*E626*E627/1000</f>
@@ -60775,7 +60775,7 @@
       </c>
       <c r="D630" s="13" t="n">
         <f aca="false">a26_lc/D629</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H630" s="7" t="s">
         <v>461</v>
@@ -60814,7 +60814,7 @@
       </c>
       <c r="D632" s="13" t="n">
         <f aca="false">$D$630*D631</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E632" s="13" t="n">
         <f aca="false">$D$630*E631</f>
@@ -60850,11 +60850,11 @@
       </c>
       <c r="F633" s="18" t="n">
         <f aca="false">F629*F632</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G633" s="18" t="n">
         <f aca="false">G629*G632</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="634" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60963,15 +60963,15 @@
       </c>
       <c r="E638" s="18" t="n">
         <f aca="false">E633+E635+E636+E637</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F638" s="18" t="n">
         <f aca="false">F633+F635+F636+F637</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G638" s="18" t="n">
         <f aca="false">G633+G635+G636+G637</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60987,7 +60987,7 @@
       </c>
       <c r="E639" s="13" t="n">
         <f aca="false">E638/D638-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F639" s="13" t="n">
         <f aca="false">F638/E638-1</f>
@@ -61043,11 +61043,11 @@
       </c>
       <c r="F641" s="17" t="n">
         <f aca="false">F633/fx/F625*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G641" s="17" t="n">
         <f aca="false">G633/fx/G625*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61151,7 +61151,7 @@
       </c>
       <c r="G646" s="18" t="n">
         <f aca="false">F646*(1+MAX(0,phi*G639))</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61179,7 +61179,7 @@
       </c>
       <c r="G647" s="18" t="n">
         <f aca="false">G646+0*G638</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61203,11 +61203,11 @@
       </c>
       <c r="F648" s="18" t="n">
         <f aca="false">F644-F647</f>
-        <v>14.8228037443267</v>
+        <v>14.8228037443268</v>
       </c>
       <c r="G648" s="18" t="n">
         <f aca="false">G644-G647</f>
-        <v>17.7900852364066</v>
+        <v>17.7900852364067</v>
       </c>
     </row>
     <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61227,7 +61227,7 @@
       </c>
       <c r="E649" s="13" t="n">
         <f aca="false">E648/E638</f>
-        <v>0.199583425893515</v>
+        <v>0.199583425893516</v>
       </c>
       <c r="F649" s="13" t="n">
         <f aca="false">F648/F638</f>
@@ -61311,7 +61311,7 @@
       </c>
       <c r="E652" s="18" t="n">
         <f aca="false">(E648+E650)*E651</f>
-        <v>9.2050691389527</v>
+        <v>9.20506913895271</v>
       </c>
       <c r="F652" s="18" t="n">
         <f aca="false">(F648+F650)*F651</f>
@@ -61367,7 +61367,7 @@
       </c>
       <c r="E654" s="19" t="n">
         <f aca="false">E652/E653</f>
-        <v>98.8975284898508</v>
+        <v>98.897528489851</v>
       </c>
       <c r="F654" s="19" t="n">
         <f aca="false">F652/F653</f>
@@ -61375,7 +61375,7 @@
       </c>
       <c r="G654" s="19" t="n">
         <f aca="false">G652/G653</f>
-        <v>137.615993227324</v>
+        <v>137.615993227325</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61391,11 +61391,11 @@
       </c>
       <c r="E655" s="13" t="n">
         <f aca="false">E654/D654-1</f>
-        <v>0.869489473717529</v>
+        <v>0.869489473717533</v>
       </c>
       <c r="F655" s="13" t="n">
         <f aca="false">F654/E654-1</f>
-        <v>0.159406685035449</v>
+        <v>0.159406685035448</v>
       </c>
       <c r="G655" s="13" t="n">
         <f aca="false">G654/F654-1</f>
@@ -61447,7 +61447,7 @@
       </c>
       <c r="D661" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E661" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61570,7 +61570,7 @@
       </c>
       <c r="D666" s="19" t="n">
         <f aca="false">D663*D664*D665/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E666" s="19" t="n">
         <f aca="false">E663*E664*E665/1000</f>
@@ -61618,7 +61618,7 @@
       </c>
       <c r="D668" s="13" t="n">
         <f aca="false">a26_lc/D667</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="H668" s="7" t="s">
         <v>461</v>
@@ -61657,7 +61657,7 @@
       </c>
       <c r="D670" s="13" t="n">
         <f aca="false">$D$668*D669</f>
-        <v>0.158700776440169</v>
+        <v>0.15870077644017</v>
       </c>
       <c r="E670" s="13" t="n">
         <f aca="false">$D$668*E669</f>
@@ -61693,11 +61693,11 @@
       </c>
       <c r="F671" s="18" t="n">
         <f aca="false">F667*F670</f>
-        <v>57.7083777630379</v>
+        <v>57.708377763038</v>
       </c>
       <c r="G671" s="18" t="n">
         <f aca="false">G667*G670</f>
-        <v>69.8476512225021</v>
+        <v>69.8476512225023</v>
       </c>
     </row>
     <row r="672" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61806,15 +61806,15 @@
       </c>
       <c r="E676" s="18" t="n">
         <f aca="false">E671+E673+E674+E675</f>
-        <v>64.0575147525855</v>
+        <v>64.0575147525856</v>
       </c>
       <c r="F676" s="18" t="n">
         <f aca="false">F671+F673+F674+F675</f>
-        <v>72.2965899177219</v>
+        <v>72.296589917722</v>
       </c>
       <c r="G676" s="18" t="n">
         <f aca="false">G671+G673+G674+G675</f>
-        <v>84.194509363078</v>
+        <v>84.1945093630781</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61830,7 +61830,7 @@
       </c>
       <c r="E677" s="13" t="n">
         <f aca="false">E676/D676-1</f>
-        <v>0.676721023036465</v>
+        <v>0.676721023036468</v>
       </c>
       <c r="F677" s="13" t="n">
         <f aca="false">F676/E676-1</f>
@@ -61886,11 +61886,11 @@
       </c>
       <c r="F679" s="17" t="n">
         <f aca="false">F671/fx/F663*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
       <c r="G679" s="17" t="n">
         <f aca="false">G671/fx/G663*1000</f>
-        <v>42.7001743744939</v>
+        <v>42.700174374494</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61994,7 +61994,7 @@
       </c>
       <c r="G684" s="18" t="n">
         <f aca="false">F684*(1+MAX(0,phi*G677))</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62022,7 +62022,7 @@
       </c>
       <c r="G685" s="18" t="n">
         <f aca="false">G684+0*G676</f>
-        <v>7.60604498322605</v>
+        <v>7.60604498322606</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62046,11 +62046,11 @@
       </c>
       <c r="F686" s="18" t="n">
         <f aca="false">F682-F685</f>
-        <v>14.8228037443267</v>
+        <v>14.8228037443268</v>
       </c>
       <c r="G686" s="18" t="n">
         <f aca="false">G682-G685</f>
-        <v>17.7900852364066</v>
+        <v>17.7900852364067</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62070,7 +62070,7 @@
       </c>
       <c r="E687" s="13" t="n">
         <f aca="false">E686/E676</f>
-        <v>0.199583425893515</v>
+        <v>0.199583425893516</v>
       </c>
       <c r="F687" s="13" t="n">
         <f aca="false">F686/F676</f>
@@ -62154,7 +62154,7 @@
       </c>
       <c r="E690" s="18" t="n">
         <f aca="false">(E686+E688)*E689</f>
-        <v>9.97215823386542</v>
+        <v>9.97215823386544</v>
       </c>
       <c r="F690" s="18" t="n">
         <f aca="false">(F686+F688)*F689</f>
@@ -62210,7 +62210,7 @@
       </c>
       <c r="E692" s="19" t="n">
         <f aca="false">E690/E691</f>
-        <v>107.138989197338</v>
+        <v>107.138989197339</v>
       </c>
       <c r="F692" s="19" t="n">
         <f aca="false">F690/F691</f>
@@ -62290,7 +62290,7 @@
       </c>
       <c r="D699" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E699" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62413,7 +62413,7 @@
       </c>
       <c r="D704" s="19" t="n">
         <f aca="false">D701*D702*D703/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E704" s="19" t="n">
         <f aca="false">E701*E702*E703/1000</f>
@@ -62532,15 +62532,15 @@
       </c>
       <c r="E709" s="18" t="n">
         <f aca="false">E705*E708</f>
-        <v>45.1139752625333</v>
+        <v>45.1139752625334</v>
       </c>
       <c r="F709" s="18" t="n">
         <f aca="false">F705*F708</f>
-        <v>52.8993462827848</v>
+        <v>52.8993462827849</v>
       </c>
       <c r="G709" s="18" t="n">
         <f aca="false">G705*G708</f>
-        <v>64.027013620627</v>
+        <v>64.0270136206271</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62653,11 +62653,11 @@
       </c>
       <c r="F714" s="18" t="n">
         <f aca="false">F709+F711+F712+F713</f>
-        <v>69.2115156810988</v>
+        <v>69.2115156810989</v>
       </c>
       <c r="G714" s="18" t="n">
         <f aca="false">G709+G711+G712+G713</f>
-        <v>80.0116311426513</v>
+        <v>80.0116311426514</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62673,7 +62673,7 @@
       </c>
       <c r="E715" s="13" t="n">
         <f aca="false">E714/D714-1</f>
-        <v>0.61686927111676</v>
+        <v>0.616869271116762</v>
       </c>
       <c r="F715" s="13" t="n">
         <f aca="false">F714/E714-1</f>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="E716" s="13" t="n">
         <f aca="false">E709/E714</f>
-        <v>0.730343072387752</v>
+        <v>0.730343072387753</v>
       </c>
       <c r="F716" s="13" t="n">
         <f aca="false">F709/F714</f>
@@ -62725,7 +62725,7 @@
       </c>
       <c r="E717" s="17" t="n">
         <f aca="false">E709/fx/E701*1000</f>
-        <v>33.8516496777252</v>
+        <v>33.8516496777253</v>
       </c>
       <c r="F717" s="17" t="n">
         <f aca="false">F709/fx/F701*1000</f>
@@ -62773,11 +62773,11 @@
       </c>
       <c r="E720" s="18" t="n">
         <f aca="false">$D$719*E714+d_lc*E709</f>
-        <v>18.4802357508027</v>
+        <v>18.4802357508028</v>
       </c>
       <c r="F720" s="18" t="n">
         <f aca="false">$D$719*F714+d_lc*F709</f>
-        <v>20.8238207825275</v>
+        <v>20.8238207825276</v>
       </c>
       <c r="G720" s="18" t="n">
         <f aca="false">$D$719*G714+d_lc*G709</f>
@@ -62805,7 +62805,7 @@
       </c>
       <c r="F721" s="13" t="n">
         <f aca="false">F720/F714</f>
-        <v>0.300872197026807</v>
+        <v>0.300872197026808</v>
       </c>
       <c r="G721" s="13" t="n">
         <f aca="false">G720/G714</f>
@@ -62829,7 +62829,7 @@
       </c>
       <c r="E722" s="18" t="n">
         <f aca="false">D722*(1+MAX(0,phi*E715))</f>
-        <v>6.16959734003604</v>
+        <v>6.16959734003605</v>
       </c>
       <c r="F722" s="18" t="n">
         <f aca="false">E722*(1+MAX(0,phi*F715))</f>
@@ -62837,7 +62837,7 @@
       </c>
       <c r="G722" s="18" t="n">
         <f aca="false">F722*(1+MAX(0,phi*G715))</f>
-        <v>7.32742147623062</v>
+        <v>7.32742147623063</v>
       </c>
     </row>
     <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62857,7 +62857,7 @@
       </c>
       <c r="E723" s="18" t="n">
         <f aca="false">E722+0*E714</f>
-        <v>6.16959734003604</v>
+        <v>6.16959734003605</v>
       </c>
       <c r="F723" s="18" t="n">
         <f aca="false">F722+0*F714</f>
@@ -62865,7 +62865,7 @@
       </c>
       <c r="G723" s="18" t="n">
         <f aca="false">G722+0*G714</f>
-        <v>7.32742147623062</v>
+        <v>7.32742147623063</v>
       </c>
     </row>
     <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62997,11 +62997,11 @@
       </c>
       <c r="E728" s="18" t="n">
         <f aca="false">(E724+E726)*E727</f>
-        <v>9.10987242396734</v>
+        <v>9.10987242396736</v>
       </c>
       <c r="F728" s="18" t="n">
         <f aca="false">(F724+F726)*F727</f>
-        <v>10.4866677931577</v>
+        <v>10.4866677931578</v>
       </c>
       <c r="G728" s="18" t="n">
         <f aca="false">(G724+G726)*G727</f>
@@ -63053,11 +63053,11 @@
       </c>
       <c r="E730" s="19" t="n">
         <f aca="false">E728/E729</f>
-        <v>97.8747529201851</v>
+        <v>97.8747529201853</v>
       </c>
       <c r="F730" s="19" t="n">
         <f aca="false">F728/F729</f>
-        <v>112.666782962959</v>
+        <v>112.66678296296</v>
       </c>
       <c r="G730" s="19" t="n">
         <f aca="false">G728/G729</f>
@@ -63077,15 +63077,15 @@
       </c>
       <c r="E731" s="13" t="n">
         <f aca="false">E730/D730-1</f>
-        <v>0.850155642117666</v>
+        <v>0.85015564211767</v>
       </c>
       <c r="F731" s="13" t="n">
         <f aca="false">F730/E730-1</f>
-        <v>0.151132233813523</v>
+        <v>0.151132233813524</v>
       </c>
       <c r="G731" s="13" t="n">
         <f aca="false">G730/F730-1</f>
-        <v>0.191821129358881</v>
+        <v>0.19182112935888</v>
       </c>
     </row>
     <row r="734" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63133,7 +63133,7 @@
       </c>
       <c r="D737" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E737" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -63256,7 +63256,7 @@
       </c>
       <c r="D742" s="19" t="n">
         <f aca="false">D739*D740*D741/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E742" s="19" t="n">
         <f aca="false">E739*E740*E741/1000</f>
@@ -63355,7 +63355,7 @@
       </c>
       <c r="G746" s="13" t="n">
         <f aca="false">$D$744*G745</f>
-        <v>0.141640442972851</v>
+        <v>0.141640442972852</v>
       </c>
     </row>
     <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63375,15 +63375,15 @@
       </c>
       <c r="E747" s="18" t="n">
         <f aca="false">E743*E746</f>
-        <v>51.6760080279927</v>
+        <v>51.6760080279928</v>
       </c>
       <c r="F747" s="18" t="n">
         <f aca="false">F743*F746</f>
-        <v>60.5937966511898</v>
+        <v>60.5937966511899</v>
       </c>
       <c r="G747" s="18" t="n">
         <f aca="false">G743*G746</f>
-        <v>73.3400337836273</v>
+        <v>73.3400337836274</v>
       </c>
     </row>
     <row r="748" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63492,15 +63492,15 @@
       </c>
       <c r="E752" s="18" t="n">
         <f aca="false">E747+E749+E750+E751</f>
-        <v>65.4294619383927</v>
+        <v>65.4294619383928</v>
       </c>
       <c r="F752" s="18" t="n">
         <f aca="false">F747+F749+F750+F751</f>
-        <v>74.1476344596958</v>
+        <v>74.1476344596959</v>
       </c>
       <c r="G752" s="18" t="n">
         <f aca="false">G747+G749+G750+G751</f>
-        <v>86.704236295334</v>
+        <v>86.7042362953341</v>
       </c>
     </row>
     <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63516,11 +63516,11 @@
       </c>
       <c r="E753" s="13" t="n">
         <f aca="false">E752/D752-1</f>
-        <v>0.712632074188289</v>
+        <v>0.712632074188291</v>
       </c>
       <c r="F753" s="13" t="n">
         <f aca="false">F752/E752-1</f>
-        <v>0.133245364748865</v>
+        <v>0.133245364748864</v>
       </c>
       <c r="G753" s="13" t="n">
         <f aca="false">G752/F752-1</f>
@@ -63552,7 +63552,7 @@
       </c>
       <c r="G754" s="13" t="n">
         <f aca="false">G747/G752</f>
-        <v>0.845864480413791</v>
+        <v>0.845864480413792</v>
       </c>
     </row>
     <row r="755" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63564,7 +63564,7 @@
       </c>
       <c r="D755" s="17" t="n">
         <f aca="false">D747/fx/D739*1000</f>
-        <v>32.1434555405718</v>
+        <v>32.1434555405719</v>
       </c>
       <c r="E755" s="17" t="n">
         <f aca="false">E747/fx/E739*1000</f>
@@ -63572,11 +63572,11 @@
       </c>
       <c r="F755" s="17" t="n">
         <f aca="false">F747/fx/F739*1000</f>
-        <v>44.8351830932186</v>
+        <v>44.8351830932187</v>
       </c>
       <c r="G755" s="17" t="n">
         <f aca="false">G747/fx/G739*1000</f>
-        <v>44.8351830932186</v>
+        <v>44.8351830932187</v>
       </c>
     </row>
     <row r="756" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63616,7 +63616,7 @@
       </c>
       <c r="E758" s="18" t="n">
         <f aca="false">$D$757*E752+d_lc*E747</f>
-        <v>19.5075550778138</v>
+        <v>19.5075550778139</v>
       </c>
       <c r="F758" s="18" t="n">
         <f aca="false">$D$757*F752+d_lc*F747</f>
@@ -63624,7 +63624,7 @@
       </c>
       <c r="G758" s="18" t="n">
         <f aca="false">$D$757*G752+d_lc*G747</f>
-        <v>26.0936147316319</v>
+        <v>26.093614731632</v>
       </c>
     </row>
     <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63672,15 +63672,15 @@
       </c>
       <c r="E760" s="18" t="n">
         <f aca="false">D760*(1+MAX(0,phi*E753))</f>
-        <v>6.44371671534442</v>
+        <v>6.44371671534443</v>
       </c>
       <c r="F760" s="18" t="n">
         <f aca="false">E760*(1+MAX(0,phi*F753))</f>
-        <v>7.00180371499279</v>
+        <v>7.0018037149928</v>
       </c>
       <c r="G760" s="18" t="n">
         <f aca="false">F760*(1+MAX(0,phi*G753))</f>
-        <v>7.77252634577827</v>
+        <v>7.77252634577828</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63700,15 +63700,15 @@
       </c>
       <c r="E761" s="18" t="n">
         <f aca="false">E760+0*E752</f>
-        <v>6.44371671534442</v>
+        <v>6.44371671534443</v>
       </c>
       <c r="F761" s="18" t="n">
         <f aca="false">F760+0*F752</f>
-        <v>7.00180371499279</v>
+        <v>7.0018037149928</v>
       </c>
       <c r="G761" s="18" t="n">
         <f aca="false">G760+0*G752</f>
-        <v>7.77252634577827</v>
+        <v>7.77252634577828</v>
       </c>
     </row>
     <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63736,7 +63736,7 @@
       </c>
       <c r="G762" s="18" t="n">
         <f aca="false">G758-G761</f>
-        <v>18.3210883858536</v>
+        <v>18.3210883858537</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63840,7 +63840,7 @@
       </c>
       <c r="E766" s="18" t="n">
         <f aca="false">(E762+E764)*E765</f>
-        <v>9.66724038822737</v>
+        <v>9.66724038822739</v>
       </c>
       <c r="F766" s="18" t="n">
         <f aca="false">(F762+F764)*F765</f>
@@ -63920,15 +63920,15 @@
       </c>
       <c r="E769" s="13" t="n">
         <f aca="false">E768/D768-1</f>
-        <v>0.963353438510323</v>
+        <v>0.963353438510326</v>
       </c>
       <c r="F769" s="13" t="n">
         <f aca="false">F768/E768-1</f>
-        <v>0.164026393838935</v>
+        <v>0.164026393838934</v>
       </c>
       <c r="G769" s="13" t="n">
         <f aca="false">G768/F768-1</f>
-        <v>0.204807448225597</v>
+        <v>0.204807448225598</v>
       </c>
     </row>
   </sheetData>

--- a/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
+++ b/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
@@ -6588,26 +6588,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6626,18 +6607,28 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D28:F28</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型的假設（唯讀）；雙鴻另做機架分歧管（</t>
+      <t xml:space="preserve">SIF_lc_mani</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Siliconomics M19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（與奇鋐模型同一值）；雙鴻另做機架分歧管（</t>
     </r>
     <r>
       <rPr>
@@ -6834,26 +6825,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6872,18 +6844,28 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D29:F29</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型的假設（唯讀）：</t>
+      <t xml:space="preserve">SIF_lc_adj_27</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Siliconomics M19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（與奇鋐模型同一值）：</t>
     </r>
     <r>
       <rPr>
@@ -7090,26 +7072,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7128,7 +7091,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D30:F30</t>
+      <t xml:space="preserve">SIF_lc_adj_28</t>
     </r>
   </si>
   <si>
@@ -7268,26 +7231,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7306,7 +7250,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D31:F31</t>
+      <t xml:space="preserve">SIF_lc_adj_29</t>
     </r>
   </si>
   <si>
@@ -7370,26 +7314,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7408,18 +7333,28 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D32:F32</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型的假設（唯讀；</t>
+      <t xml:space="preserve">SIF_lc_pen_26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Siliconomics M19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（與奇鋐模型同一值；</t>
     </r>
     <r>
       <rPr>
@@ -7654,26 +7589,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7692,7 +7608,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D33:F33</t>
+      <t xml:space="preserve">SIF_lc_pen_27</t>
     </r>
   </si>
   <si>
@@ -7756,26 +7672,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7794,7 +7691,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D34:F34</t>
+      <t xml:space="preserve">SIF_lc_pen_28</t>
     </r>
   </si>
   <si>
@@ -7858,26 +7755,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7896,7 +7774,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D35:F35</t>
+      <t xml:space="preserve">SIF_lc_pen_29</t>
     </r>
   </si>
   <si>
@@ -7941,26 +7819,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7979,7 +7838,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D36:F36</t>
+      <t xml:space="preserve">SIF_lc_avrel_27</t>
     </r>
     <r>
       <rPr>
@@ -8215,26 +8074,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8253,7 +8093,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D37:F37</t>
+      <t xml:space="preserve">SIF_lc_avrel_28</t>
     </r>
     <r>
       <rPr>
@@ -8307,26 +8147,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8345,7 +8166,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D38:F38</t>
+      <t xml:space="preserve">SIF_lc_avrel_29</t>
     </r>
     <r>
       <rPr>
@@ -36699,7 +36520,7 @@
       <c r="H24" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="7" t="s">
         <v>99</v>
       </c>
     </row>
@@ -36728,7 +36549,7 @@
       <c r="H25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="7" t="s">
         <v>103</v>
       </c>
     </row>
@@ -36815,7 +36636,7 @@
       <c r="H28" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="7" t="s">
         <v>113</v>
       </c>
     </row>
@@ -38123,7 +37944,7 @@
         <v>50</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>31</v>
@@ -38192,7 +38013,7 @@
         <v>50</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>31</v>
@@ -39470,7 +39291,7 @@
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">avsh_26</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">avsh_27</f>
@@ -39482,7 +39303,7 @@
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">avsh_29</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>423</v>
@@ -39497,7 +39318,7 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">C8+C9</f>
-        <v>0.657628417556846</v>
+        <v>0.657628417556847</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">D8+D9</f>
@@ -39509,7 +39330,7 @@
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">F8+F9</f>
-        <v>0.558984154923319</v>
+        <v>0.55898415492332</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>425</v>
@@ -39524,7 +39345,7 @@
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">1-C10</f>
-        <v>0.342371582443154</v>
+        <v>0.342371582443153</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">1-D10</f>
@@ -39536,7 +39357,7 @@
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">1-F10</f>
-        <v>0.441015845076681</v>
+        <v>0.44101584507668</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46319,15 +46140,15 @@
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">avsh_26+PL!D72</f>
-        <v>0.657628417556846</v>
+        <v>0.657628417556847</v>
       </c>
       <c r="E19" s="13" t="n">
         <f aca="false">avsh_26+PL!D110</f>
-        <v>0.657628417556846</v>
+        <v>0.657628417556847</v>
       </c>
       <c r="G19" s="13" t="n">
         <f aca="false">avsh_26+PL!D148</f>
-        <v>0.657628417556846</v>
+        <v>0.657628417556847</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>687</v>
@@ -46388,15 +46209,15 @@
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">avsh_29+PL!G72</f>
-        <v>0.590724310211353</v>
+        <v>0.590724310211354</v>
       </c>
       <c r="E22" s="13" t="n">
         <f aca="false">avsh_29+PL!G110</f>
-        <v>0.558984154923319</v>
+        <v>0.55898415492332</v>
       </c>
       <c r="G22" s="13" t="n">
         <f aca="false">avsh_29+PL!G148</f>
-        <v>0.535179038457294</v>
+        <v>0.535179038457295</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>687</v>

--- a/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
+++ b/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
@@ -5720,26 +5720,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5919,26 +5919,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6040,26 +6040,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6161,26 +6161,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6282,26 +6282,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6403,26 +6403,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
+++ b/auras/dist/20261025_雙鴻模型_v0.1.1.xlsx
@@ -5005,26 +5005,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6489,26 +6489,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13371,26 +13371,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
